--- a/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -656,405 +656,418 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E7" s="2">
         <v>45136</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45045</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44863</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44772</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44590</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44499</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44317</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44226</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44044</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43953</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43862</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43771</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43680</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43589</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43498</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43407</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43316</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43225</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43134</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43036</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42945</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42854</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42763</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4924700</v>
+      </c>
+      <c r="E8" s="3">
         <v>4963500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4723100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4929600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4785300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5103800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4496400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4357800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4264100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4177200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3868200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3946600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3731700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3954100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3797600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3472300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3229400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3345800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3143100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3416900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3221700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3307100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3061700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3556000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3084200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3167500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2946800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3229800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2986200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4022200</v>
+      </c>
+      <c r="E9" s="3">
         <v>4066700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3843200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4026400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3908200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4243800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3705800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3560600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3472900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3413600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3141500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3204000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2988400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3197800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3060900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2850100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2611800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2733100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2569000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2787900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2629600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2718600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2510300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2934700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2523300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2614200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2441300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2681700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2456200</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>902500</v>
+      </c>
+      <c r="E10" s="3">
         <v>896800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>880000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>903200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>877100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>860000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>790600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>797200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>791200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>763600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>726700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>742600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>743300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>756300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>736700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>622200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>617600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>612700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>574100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>629000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>592100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>588500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>551400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>621300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>560900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>553300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>505500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>548100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,8 +1099,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,8 +1189,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,32 +1281,35 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7900</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1297,37 +1317,37 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>2800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>15100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1353,8 +1373,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1442,8 +1465,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1498,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4725300</v>
+      </c>
+      <c r="E17" s="3">
         <v>4763300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4536400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4736800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4593400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4900900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4346100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4200700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4093900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4013400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3742600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3801900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3544100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3791800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3653900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3392300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3130500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3247100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3072500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3307000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3131300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3268400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2997100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3463300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3003700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3092700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2974600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3166900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2933100</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>199400</v>
+      </c>
+      <c r="E18" s="3">
         <v>200200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>186700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>192800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>191900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>202900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>150300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>157100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>170200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>163800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>125600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>144700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>187600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>162300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>143700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>80000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>98900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>98700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>70600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>109900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>90400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>38700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>64600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>92700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>80500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>74800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-27800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>62900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,8 +1716,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1707,25 +1741,25 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5600</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-500</v>
       </c>
       <c r="Q20" s="3">
         <v>-500</v>
@@ -1734,13 +1768,13 @@
         <v>-500</v>
       </c>
       <c r="S20" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="T20" s="3">
         <v>-600</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -1772,364 +1806,379 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>256800</v>
+      </c>
+      <c r="E21" s="3">
         <v>255100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>241000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>244500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>244100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>252900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>197400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>202500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>216500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>205700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>164900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>185700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>224100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>203100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>184100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>119600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>137500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>137100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>109400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>149700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>130300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>79800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>106000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>133400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>121700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>116000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>13300</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E22" s="3">
         <v>16300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7800</v>
-      </c>
-      <c r="J22" s="3">
-        <v>12400</v>
       </c>
       <c r="K22" s="3">
         <v>12400</v>
       </c>
       <c r="L22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="M22" s="3">
         <v>12900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>17500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>23600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>25000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>26200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>27800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>26700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>33000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>59600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>45200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>46500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>42300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>43800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>64100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>35400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>35500</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>181400</v>
+      </c>
+      <c r="E23" s="3">
         <v>184000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>172100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>176500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>179500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>192000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>142500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>145300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>158300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>147400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>107000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>128800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>164500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>142900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>121900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>55900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>73200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>72000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>42900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>83100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>57300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-20900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>19400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>46200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>38200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>31000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-91900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>27500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E24" s="3">
         <v>52700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>56100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>47100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>48100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>51000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>30000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>37700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>31700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>36400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>25400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>32900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>41600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>36200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>26200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>18000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>17700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>19400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-15400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>10200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>15300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>11100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-33100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>10800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2266,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>130500</v>
+      </c>
+      <c r="E26" s="3">
         <v>131300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>116000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>129400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>131400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>141000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>112500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>107600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>126600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>111000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>81600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>95900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>122900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>106700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>95700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>42200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>55200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>54300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>36100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>63700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>52200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>14300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>36000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>22900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>19800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-58800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>16700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>130500</v>
+      </c>
+      <c r="E27" s="3">
         <v>131300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>116000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>129400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>131400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>141000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>112500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>107600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>126600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>111000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>81600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>95900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>122900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>106700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>95700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>42200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>55200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>54300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>36100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>63700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>52200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>14300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>36000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>22900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>19800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-58800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>16700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2542,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2493,17 +2554,17 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-1500</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
@@ -2511,11 +2572,11 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-100</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -2523,43 +2584,43 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P29" s="3">
         <v>-100</v>
       </c>
       <c r="Q29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>2300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-100</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>30700</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>-100</v>
       </c>
       <c r="AB29" s="3">
         <v>-100</v>
@@ -2573,8 +2634,11 @@
       <c r="AE29" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2726,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,8 +2818,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2775,25 +2845,25 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5600</v>
-      </c>
-      <c r="P32" s="3">
-        <v>500</v>
       </c>
       <c r="Q32" s="3">
         <v>500</v>
@@ -2802,13 +2872,13 @@
         <v>500</v>
       </c>
       <c r="S32" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="T32" s="3">
         <v>600</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
@@ -2840,97 +2910,103 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>130500</v>
+      </c>
+      <c r="E33" s="3">
         <v>131300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>116100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>129800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>129900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>141000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>112500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>107600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>126500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>111000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>81600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>95900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>122800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>106600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>95700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>41800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>55100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>54500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>64300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>54400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>14100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>66700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>22800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>19700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-58900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>16600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3094,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>130500</v>
+      </c>
+      <c r="E35" s="3">
         <v>131300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>116100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>129800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>129900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>141000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>112500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>107600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>126500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>111000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>81600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>95900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>122800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>106600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>95700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>41800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>55100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>54500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>64300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>54400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>14100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>66700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>22800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>19700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-58900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>16600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E38" s="2">
         <v>45136</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45045</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44863</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44772</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44590</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44499</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44317</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44226</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44044</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43953</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43862</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43771</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43680</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43589</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43498</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43407</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43316</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43225</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43134</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43036</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42945</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42854</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42763</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3319,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,80 +3353,81 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E41" s="3">
         <v>26200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>163700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>38000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>45400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>84700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>42400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>63000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>43500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>46100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>168800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>132900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>30200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>30000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>29100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>29900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>27100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>31500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>31300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>30500</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3356,8 +3443,11 @@
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3445,80 +3535,83 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>224500</v>
+      </c>
+      <c r="E43" s="3">
         <v>200300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>217900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>239700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>252000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>204500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>210400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>174000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>200300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>169100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>198000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>172700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>188400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>170600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>193900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>206400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>186000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>162300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>180400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>194300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>179100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>165300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>168700</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3534,80 +3627,83 @@
       <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1661900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1540500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1532000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1378600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1504400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1376500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1462100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1242900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1255700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1033600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1120300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1205700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1264300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1005300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1024900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1081500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1271200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1026500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1085600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1052300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1245100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1005000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1055200</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3623,80 +3719,83 @@
       <c r="AE44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E45" s="3">
         <v>76300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>69000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>51000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>72300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>57800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>58800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>54700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>58600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>46400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>54300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>48600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>97100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>64100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>46600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>42000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>55300</v>
-      </c>
-      <c r="T45" s="3">
-        <v>47400</v>
       </c>
       <c r="U45" s="3">
         <v>47400</v>
       </c>
       <c r="V45" s="3">
+        <v>47400</v>
+      </c>
+      <c r="W45" s="3">
         <v>63500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>104300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>107300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>83000</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3712,80 +3811,83 @@
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2000500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1843300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1842300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1703200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1863300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1802500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1769300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1517100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1599300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1291600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1435500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1470600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1596000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1408800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1398400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1360000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1542400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1265300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1343200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1337200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1560000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1309000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1337500</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3801,8 +3903,11 @@
       <c r="AE46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3890,80 +3995,83 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3670600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3593700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3489400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3480000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3459700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3424700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3167400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3074300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3032200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2980200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2934900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2856600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2804000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2799400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2841200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2820300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2843300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2791600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2784500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>748800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>745900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>747700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>749700</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3979,80 +4087,83 @@
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1118400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1120400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1122400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1124300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1126600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1128900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1046500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1048800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1051400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1054000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1056600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1059300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1062200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1065200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1068200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1071100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1074500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1077900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1081200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1125000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1130800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1136700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1142800</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4068,8 +4179,11 @@
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4271,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,80 +4363,83 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E52" s="3">
         <v>46500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>40400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>42400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>29300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>20700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>20400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17800</v>
-      </c>
-      <c r="V52" s="3">
-        <v>28300</v>
       </c>
       <c r="W52" s="3">
         <v>28300</v>
       </c>
       <c r="X52" s="3">
+        <v>28300</v>
+      </c>
+      <c r="Y52" s="3">
         <v>27400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>31400</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4335,8 +4455,11 @@
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,80 +4547,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6837200</v>
+      </c>
+      <c r="E54" s="3">
         <v>6603900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6494500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6350000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6478900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6387200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6010000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5668900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5710200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5347600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5449200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5411500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5482300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5294000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5328100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5269800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5478100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5152100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5226700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3239300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3465000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3220900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3261300</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4513,8 +4639,11 @@
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4675,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,80 +4709,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1319000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1226500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1281700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1195700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1363700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1243300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1267100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1112800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1235800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1029700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1023100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>988100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1176100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1004700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>990400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>786400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>973300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>798500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>820500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>816900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>976500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>783100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>799500</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4668,32 +4799,35 @@
       <c r="AE57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>434000</v>
+      </c>
+      <c r="E58" s="3">
         <v>411000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>400000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>405000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>295000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>350000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>80000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -4701,47 +4835,47 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>210000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>260000</v>
       </c>
       <c r="O58" s="3">
         <v>260000</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>15400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>343400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>449400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>195400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>246400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>254400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>389400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>62300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>179300</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4757,80 +4891,83 @@
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>986100</v>
+      </c>
+      <c r="E59" s="3">
         <v>953700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>937700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>944600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>941200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>890900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>862000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>889700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>868300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>809500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>802800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>783100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>774300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>759500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>714400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>671600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>629100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>617200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>607000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>506400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>487900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>475600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>461200</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4846,80 +4983,83 @@
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2739100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2591100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2619300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2545300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2600000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2484100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2209100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2002500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2104100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1839200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2035900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2031200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2210400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1764200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1720200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1801400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2051800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1611100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1673900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1577700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1853800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1321000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1440000</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4935,80 +5075,83 @@
       <c r="AE60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>398400</v>
+      </c>
+      <c r="E61" s="3">
         <v>448100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>448000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>447900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>600100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>699400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>749000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>748600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>748100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>747700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>747300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>846200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>845700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1202200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1334800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1337300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1339700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1540600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1543500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1546500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1549400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1894100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2508000</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5024,80 +5167,83 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2346100</v>
+      </c>
+      <c r="E62" s="3">
         <v>2333300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2295400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2309900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2335900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2350100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2330600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2269700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2290300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2272300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2252400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2214800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2208800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2208500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2240600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2185400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2191100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2165000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2157600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>317200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>318400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>323700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>324700</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5113,8 +5259,11 @@
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5351,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5443,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,80 +5535,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5483500</v>
+      </c>
+      <c r="E66" s="3">
         <v>5372600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5362800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5303100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5536000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5533700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5288700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5020800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5142500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4859200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5035700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5092200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5264900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5174900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5295600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5324100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5582600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5316700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5375000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3441400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3721600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3538700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4272700</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5469,8 +5627,11 @@
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5663,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5753,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +5845,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +5937,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,80 +6029,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1022400</v>
+      </c>
+      <c r="E72" s="3">
         <v>891900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>760600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>644500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>514700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>384800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>243800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>131300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-102800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-213800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-295300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-391200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-514000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-620600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-716400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-758100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-813200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-867700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-915100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-979400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1033900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1028200</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5947,8 +6121,11 @@
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6213,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6305,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,80 +6397,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1353700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1231300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1131700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1046800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>942900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>853600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>721300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>648100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>567700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>488400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>413500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>319300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>217400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>119100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>32500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-54300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-104500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-164600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-148300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-202100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-256600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-317900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-1011400</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6303,8 +6489,11 @@
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6581,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45227</v>
+      </c>
+      <c r="E80" s="2">
         <v>45136</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45045</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44863</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44772</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44590</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44499</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44317</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44226</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44044</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43953</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43862</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43771</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43680</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43589</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43498</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43407</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43316</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43225</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43134</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43036</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42945</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42854</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42763</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>130500</v>
+      </c>
+      <c r="E81" s="3">
         <v>131300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>116100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>129800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>129900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>141000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>112500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>107600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>126500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>111000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>81600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>95900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>122800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>106600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>95700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>41800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>55100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>54500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>64300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>54400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>14100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>66700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>22800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>19700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-58900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>16600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,97 +6806,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E83" s="3">
         <v>54800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>54200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>51700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>52200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>50000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>47100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>44900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>44400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>43100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>42200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>41300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>40800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>40100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>39200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>39000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>38700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>39800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>39900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>41100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>41400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>40700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>41100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>41200</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +6988,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7080,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7172,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7264,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7356,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E89" s="3">
         <v>150400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>119100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>175300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>169800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>398700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>44300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>98500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>173900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>310300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>249000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>66600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>68300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>263800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>469900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>133600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>170200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>44900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>176200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>47700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>137900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>65400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>109700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>46400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>119100</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,97 +7484,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-133700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-122200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-92100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-103500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-102800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-101000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-90500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-101100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-74700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-73100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-74700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-65500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-69800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-35200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-52500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-56100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-51800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-36500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-42600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-27700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-33500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-42100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-51300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-21800</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7666,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7758,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-127400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-116200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-92100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-87300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-94400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-474800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-90500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-101100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-74700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-70700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-58100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-65500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-48000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-43700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-35200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-30900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-56100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-51800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-36500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-42600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-27700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-33500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-42100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-51300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,8 +7886,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7728,22 +7962,25 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-100</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8068,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8160,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,97 +8252,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-40300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-31400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-37600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-88700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-204500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>201800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>38700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-36600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-56900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-260200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-171500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-143000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-184200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-332000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-102500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>50600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-119200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-138000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-19800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-103500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-27700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-96100</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8187,93 +8436,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-129000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>125700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-39300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>42300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-122700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>35900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>102700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1200</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -656,418 +656,444 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F7" s="2">
         <v>45227</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45136</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45045</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44954</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44863</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44772</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44590</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44499</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44317</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44226</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44044</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43953</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43862</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43771</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43680</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43589</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43498</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43407</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43316</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43225</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43134</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43036</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42945</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42854</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42763</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4918500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5357300</v>
+      </c>
+      <c r="F8" s="3">
         <v>4924700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4963500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>4723100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4929600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>4785300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5103800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4496400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4357800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>4264100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4177200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3868200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3946600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3731700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3954100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3797600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>3472300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3229400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>3345800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3143100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3416900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3221700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3307100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3061700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>3556000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3084200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3167500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2946800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>3229800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2986200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4035100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4394000</v>
+      </c>
+      <c r="F9" s="3">
         <v>4022200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>4066700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3843200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>4026400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3908200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>4243800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3705800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3560600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3472900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3413600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>3141500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3204000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2988400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3197800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3060900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2850100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2611800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2733100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2569000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2787900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2629600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2718600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2510300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2934700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2523300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2614200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>2441300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>2681700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>2456200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>883400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>963300</v>
+      </c>
+      <c r="F10" s="3">
         <v>902500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>896800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>880000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>903200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>877100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>860000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>790600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>797200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>791200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>763600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>726700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>742600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>743300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>756300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>736700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>622200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>617600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>612700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>574100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>629000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>592100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>588500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>551400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>621300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>560900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>553300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>505500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>548100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1100,8 +1126,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,8 +1220,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1284,76 +1318,82 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+        <v>1800</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K14" s="3">
         <v>3600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>7900</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>2800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>1300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>15100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>2000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1376,8 +1416,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1468,8 +1514,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1499,192 +1551,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4725300</v>
+        <v>4757800</v>
       </c>
       <c r="E17" s="3">
+        <v>5143300</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4727200</v>
+      </c>
+      <c r="G17" s="3">
         <v>4763300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4536400</v>
       </c>
-      <c r="G17" s="3">
-        <v>4736800</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4593400</v>
-      </c>
       <c r="I17" s="3">
+        <v>4739400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4593600</v>
+      </c>
+      <c r="K17" s="3">
         <v>4900900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4346100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4200700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4093900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4013400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3742600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3801900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3544100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3791800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3653900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3392300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3130500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3247100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3072500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3307000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3131300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3268400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2997100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3463300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3003700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3092700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2974600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3166900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2933100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>199400</v>
+        <v>160700</v>
       </c>
       <c r="E18" s="3">
+        <v>214000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>197500</v>
+      </c>
+      <c r="G18" s="3">
         <v>200200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>186700</v>
       </c>
-      <c r="G18" s="3">
-        <v>192800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>191900</v>
-      </c>
       <c r="I18" s="3">
+        <v>190200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>191700</v>
+      </c>
+      <c r="K18" s="3">
         <v>202900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>150300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>157100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>170200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>163800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>125600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>144700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>187600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>162300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>143700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>80000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>98900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>98700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>70600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>109900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>90400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>38700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>64600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>92700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>80500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>74800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-27800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>62900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1717,8 +1783,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1744,44 +1812,44 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-3600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-5600</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-500</v>
       </c>
       <c r="S20" s="3">
         <v>-500</v>
       </c>
       <c r="T20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V20" s="3">
         <v>-600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-600</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1809,376 +1877,406 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>256800</v>
+        <v>224200</v>
       </c>
       <c r="E21" s="3">
+        <v>275300</v>
+      </c>
+      <c r="F21" s="3">
+        <v>255000</v>
+      </c>
+      <c r="G21" s="3">
         <v>255100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>241000</v>
       </c>
-      <c r="G21" s="3">
-        <v>244500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>244100</v>
-      </c>
       <c r="I21" s="3">
+        <v>241900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>243800</v>
+      </c>
+      <c r="K21" s="3">
         <v>252900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>197400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>202500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>216500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>205700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>164900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>185700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>224100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>203100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>184100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>119600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>137500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>137100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>109400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>149700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>130300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>79800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>106000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>133400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>121700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>116000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>13300</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="E22" s="3">
-        <v>16300</v>
+        <v>15600</v>
       </c>
       <c r="F22" s="3">
-        <v>14700</v>
+        <v>16200</v>
       </c>
       <c r="G22" s="3">
         <v>16300</v>
       </c>
       <c r="H22" s="3">
-        <v>12500</v>
+        <v>14700</v>
       </c>
       <c r="I22" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J22" s="3">
+        <v>12200</v>
+      </c>
+      <c r="K22" s="3">
         <v>10900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>7800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>12400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>12400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>12900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>13600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>13800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>17500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>18900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>21300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>23600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>25000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>26200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>27800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>26700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>33000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>59600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>45200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>46500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>42300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>43800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>64100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>35400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>35500</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>146800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>198400</v>
+      </c>
+      <c r="F23" s="3">
         <v>181400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>184000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>172100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>176500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>179500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>192000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>142500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>145300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>158300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>147400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>107000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>128800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>164500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>142900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>121900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>55900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>73200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>72000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>42900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>83100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>57300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-20900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>19400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>46200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>38200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>31000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-91900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>27500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>52600</v>
+      </c>
+      <c r="F24" s="3">
         <v>50900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>52700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>56100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>47100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>48100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>51000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>30000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>37700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>31700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>36400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>25400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>32900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>41600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>36200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>26200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>13700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>18000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>17700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>6800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>19400</v>
-      </c>
-      <c r="X24" s="3">
-        <v>5100</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>-15400</v>
       </c>
       <c r="Z24" s="3">
         <v>5100</v>
       </c>
       <c r="AA24" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>10200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>15300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>11100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-33100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>10800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2269,192 +2367,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>145900</v>
+      </c>
+      <c r="F26" s="3">
         <v>130500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>131300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>116000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>129400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>131400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>141000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>112500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>107600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>126600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>111000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>81600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>95900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>122900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>106700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>95700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>42200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>55200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>54300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>36100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>63700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>52200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>14300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>36000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>22900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>19800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-58800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>16700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>145900</v>
+      </c>
+      <c r="F27" s="3">
         <v>130500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>131300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>116000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>129400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>131400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>141000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>112500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>107600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>126600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>111000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>81600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>95900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>122900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>106700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>95700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>42200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>55200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>54300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>36100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>63700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>52200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>14300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>36000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>22900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>19800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-58800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>16700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2545,8 +2661,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2557,76 +2679,76 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="I29" s="3">
         <v>400</v>
       </c>
-      <c r="H29" s="3">
+      <c r="J29" s="3">
         <v>-1500</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-100</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-100</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>-100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>-300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>2300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>-100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>30700</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>-100</v>
       </c>
       <c r="AD29" s="3">
         <v>-100</v>
@@ -2637,8 +2759,14 @@
       <c r="AF29" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2729,8 +2857,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2821,8 +2955,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2848,44 +2988,44 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>3600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>5600</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>500</v>
       </c>
       <c r="S32" s="3">
         <v>500</v>
       </c>
       <c r="T32" s="3">
+        <v>500</v>
+      </c>
+      <c r="U32" s="3">
+        <v>500</v>
+      </c>
+      <c r="V32" s="3">
         <v>600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>600</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2913,100 +3053,112 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>145900</v>
+      </c>
+      <c r="F33" s="3">
         <v>130500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>131300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>116100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>129800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>129900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>141000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>112500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>107600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>126500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>111000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>81600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>95900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>122800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>106600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>95700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>41800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>55100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>54500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>35800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>64300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>54400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>14100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>66700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>22800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>19700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-58900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>16600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3097,197 +3249,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>145900</v>
+      </c>
+      <c r="F35" s="3">
         <v>130500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>131300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>116100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>129800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>129900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>141000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>112500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>107600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>126500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>111000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>81600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>95900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>122800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>106600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>95700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>41800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>55100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>54500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>35800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>64300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>54400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>14100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>66700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>22800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>19700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-58900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>16600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F38" s="2">
         <v>45227</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45136</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45045</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44954</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44863</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44772</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44590</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44499</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44317</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44226</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44044</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43953</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43862</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43771</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43680</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43589</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43498</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43407</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43316</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43225</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43134</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43036</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42945</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42854</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42763</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3320,8 +3490,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3354,86 +3526,88 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F41" s="3">
         <v>33600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>26200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>23400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>33900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>34600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>163700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>38000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>45400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>84700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>42400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>63000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>43500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>46100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>168800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>132900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>30200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>30000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>29100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>29900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>27100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>31500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>31300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>30500</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3446,8 +3620,14 @@
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3538,86 +3718,92 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>225200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>234800</v>
+      </c>
+      <c r="F43" s="3">
         <v>224500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>200300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>217900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>239700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>252000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>204500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>210400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>174000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>200300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>169100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>198000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>172700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>188400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>170600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>193900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>206400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>186000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>162300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>180400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>194300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>179100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>165300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>168700</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3630,86 +3816,92 @@
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1533300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1454800</v>
+      </c>
+      <c r="F44" s="3">
         <v>1661900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1540500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1532000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1378600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1504400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1376500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1462100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1242900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1255700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1033600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1120300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1205700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1264300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1005300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1024900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1081500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1271200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1026500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>1085600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1052300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1245100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1005000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1055200</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3722,86 +3914,92 @@
       <c r="AF44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>68400</v>
+      </c>
+      <c r="F45" s="3">
         <v>80600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>76300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>69000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>51000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>72300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>57800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>58800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>54700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>58600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>46400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>54300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>48600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>97100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>64100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>46600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>42000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>55300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>47400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>47400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>63500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>104300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>107300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>83000</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3814,86 +4012,92 @@
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1878700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1794000</v>
+      </c>
+      <c r="F46" s="3">
         <v>2000500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1843300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1842300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1703200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1863300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1802500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1769300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1517100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1599300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1291600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1435500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1470600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1596000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1408800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1398400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1360000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1542400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1265300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1343200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1337200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1560000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1309000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1337500</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3906,8 +4110,14 @@
       <c r="AF46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3998,86 +4208,92 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3780200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3719300</v>
+      </c>
+      <c r="F48" s="3">
         <v>3670600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3593700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3489400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3480000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3459700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3424700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3167400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3074300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3032200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2980200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2934900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2856600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2804000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2799400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2841200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2820300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2843300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2791600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2784500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>748800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>745900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>747700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>749700</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4090,86 +4306,92 @@
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1114800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1116400</v>
+      </c>
+      <c r="F49" s="3">
         <v>1118400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1120400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1122400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1124300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1126600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1128900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1046500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1048800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1051400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1054000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1056600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1059300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1062200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1065200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1068200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1071100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1074500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1077900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1081200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1125000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1130800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1136700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1142800</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4182,8 +4404,14 @@
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4274,8 +4502,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4366,86 +4600,92 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>47900</v>
+      </c>
+      <c r="F52" s="3">
         <v>47800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>46500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>40400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>42400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>29300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>31100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>26800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>28700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>27400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>21800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>22100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>25100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>20100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>20700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>20400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>18400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>17900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>17400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>17800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>28300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>28300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>27400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>31400</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4458,8 +4698,14 @@
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4550,86 +4796,92 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6824700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6677600</v>
+      </c>
+      <c r="F54" s="3">
         <v>6837200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6603900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6494500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6350000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>6478900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>6387200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>6010000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5668900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>5710200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5347600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5449200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5411500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5482300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5294000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>5328100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>5269800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>5478100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>5152100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5226700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3239300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3465000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3220900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3261300</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4642,8 +4894,14 @@
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4676,8 +4934,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4710,86 +4970,88 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1264900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1183300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1319000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1226500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1281700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1195700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1363700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1243300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1267100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1112800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1235800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1029700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1023100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>988100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1176100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1004700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>990400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>786400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>973300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>798500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>820500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>816900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>976500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>783100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>799500</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4802,86 +5064,92 @@
       <c r="AF57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>319000</v>
+      </c>
+      <c r="F58" s="3">
         <v>434000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>411000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>400000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>405000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>295000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>350000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>80000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>210000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>260000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>260000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>15400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>343400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>449400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>195400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>246400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>254400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>389400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>62300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>179300</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4894,86 +5162,92 @@
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>991000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>965800</v>
+      </c>
+      <c r="F59" s="3">
         <v>986100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>953700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>937700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>944600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>941200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>890900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>862000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>889700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>868300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>809500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>802800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>783100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>774300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>759500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>714400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>671600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>629100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>617200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>607000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>506400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>487900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>475600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>461200</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4986,86 +5260,92 @@
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2525800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2468000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2739100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2591100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2619300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2545300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2600000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2484100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2209100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2002500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2104100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1839200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2035900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2031200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2210400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1764200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1720200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1801400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2051800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1611100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1673900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1577700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1853800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1321000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1440000</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5078,86 +5358,92 @@
       <c r="AF60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>398500</v>
+      </c>
+      <c r="E61" s="3">
         <v>398400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
+        <v>398400</v>
+      </c>
+      <c r="G61" s="3">
         <v>448100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>448000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>447900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>600100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>699400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>749000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>748600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>748100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>747700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>747300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>846200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>845700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1202200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1334800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1337300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1339700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1540600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1543500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1546500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1549400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1894100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2508000</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5170,86 +5456,92 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2373000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2352300</v>
+      </c>
+      <c r="F62" s="3">
         <v>2346100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2333300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2295400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2309900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2335900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2350100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2330600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2269700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2290300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2272300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2252400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2214800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2208800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2208500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2240600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2185400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2191100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2165000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2157600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>317200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>318400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>323700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>324700</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5262,8 +5554,14 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5354,8 +5652,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5446,8 +5750,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5538,86 +5848,92 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5297300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5218800</v>
+      </c>
+      <c r="F66" s="3">
         <v>5483500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5372600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5362800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5303100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5536000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5533700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5288700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5020800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5142500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4859200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5035700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5092200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5264900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>5174900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5295600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5324100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>5582600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>5316700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>5375000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3441400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>3721600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>3538700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>4272700</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5630,8 +5946,14 @@
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5664,8 +5986,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5756,8 +6080,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5848,8 +6178,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5940,8 +6276,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6032,86 +6374,92 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1279300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1168200</v>
+      </c>
+      <c r="F72" s="3">
         <v>1022400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>891900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>760600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>644500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>514700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>384800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>243800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>131300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>23700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-102800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-213800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-295300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-391200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-514000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-620600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-716400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-758100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-813200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-867700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-915100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-979400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-1033900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-1028200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6124,8 +6472,14 @@
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6216,8 +6570,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6308,8 +6668,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6400,86 +6766,92 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1527400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1458900</v>
+      </c>
+      <c r="F76" s="3">
         <v>1353700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1231300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1131700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1046800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>942900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>853600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>721300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>648100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>567700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>488400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>413500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>319300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>217400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>119100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>32500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-54300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-104500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-164600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-148300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-202100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-256600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-317900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-1011400</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6492,8 +6864,14 @@
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6584,197 +6962,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45416</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45325</v>
+      </c>
+      <c r="F80" s="2">
         <v>45227</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45136</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45045</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44954</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44863</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44772</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44590</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44499</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44317</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44226</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44044</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43953</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43862</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43771</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43680</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43589</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43498</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43407</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43316</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43225</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43134</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43036</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42945</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42854</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42763</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>145900</v>
+      </c>
+      <c r="F81" s="3">
         <v>130500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>131300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>116100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>129800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>129900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>141000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>112500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>107600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>126500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>111000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>81600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>95900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>122800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>106600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>95700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>41800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>55100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>54500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>35800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>64300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>54400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>14100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>66700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>22800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>19700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-58900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>16600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6807,100 +7203,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>61300</v>
+      </c>
+      <c r="F83" s="3">
         <v>57400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>54800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>54200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>51700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>52200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>50000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>47100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>44900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>45800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>45400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>44400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>43100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>42200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>41300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>40800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>40100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>39200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>39000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>38700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>39800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>39900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>41100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>41400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>40700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>41100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>41200</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6991,8 +7395,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7083,8 +7493,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7175,8 +7591,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7267,8 +7689,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7359,100 +7787,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>274400</v>
+      </c>
+      <c r="F89" s="3">
         <v>175000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>150400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>119100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>175300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>169800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>398700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>44300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>98500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>173900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>310300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>249000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>66600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>68300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>263800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>469900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>133600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>6400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>170200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>44900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>176200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>47700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>137900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>65400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>109700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>46400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>119100</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7485,100 +7925,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-105700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-119100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-133700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-122200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-92100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-103500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-102800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-101000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-90500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-101100</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-74700</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-73100</v>
       </c>
       <c r="N91" s="3">
         <v>-74700</v>
       </c>
       <c r="O91" s="3">
+        <v>-73100</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-65500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-69800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-47800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-35200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-52500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-56100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-51800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-36500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-42600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-27700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-33500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-51300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-21800</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7669,8 +8117,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7761,100 +8215,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-105700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-119100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-127400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-116200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-92100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-87300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-94400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-474800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-90500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-101100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-74700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-70700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-58100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-65500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-48000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-43700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-35200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-30900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-56100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-51800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-36500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-42600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-27700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-33500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-42100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-51300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7887,8 +8353,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7965,22 +8433,28 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-100</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8071,8 +8545,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8163,8 +8643,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8255,100 +8741,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-96100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-152700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-40300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-31400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-37600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-88700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-204500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>201800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>38700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-36600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-56900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-260200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-171500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-3600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-143000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-184200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-332000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-102500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>50600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-119200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-5700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-138000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-19800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-103500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-27700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-96100</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8439,96 +8937,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F102" s="3">
         <v>7300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>2800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-10500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-129000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>125700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-7500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-39300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>42300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-20500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>19400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-122700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>35900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>102700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-4400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>3200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>1200</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -656,444 +656,457 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E7" s="2">
         <v>45416</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45325</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45227</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45136</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45045</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44954</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44863</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44772</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44590</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44499</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44317</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44226</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44044</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43953</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43862</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43771</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43680</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43589</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43498</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43407</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43316</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43225</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43134</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43036</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42945</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42854</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42763</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5205400</v>
+      </c>
+      <c r="E8" s="3">
         <v>4918500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5357300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4924700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4963500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4723100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4929600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4785300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5103800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4496400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4357800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4264100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4177200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3868200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3946600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3731700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3954100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3797600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3472300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3229400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3345800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3143100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3416900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3221700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3307100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3061700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3556000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3084200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3167500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2946800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3229800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2986200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4248800</v>
+      </c>
+      <c r="E9" s="3">
         <v>4035100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4394000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4022200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4066700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3843200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4026400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3908200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4243800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3705800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3560600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3472900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3413600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3141500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3204000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2988400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3197800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3060900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2850100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2611800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2733100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2569000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2787900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2629600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2718600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2510300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2934700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2523300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2614200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2441300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2681700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2456200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>956600</v>
+      </c>
+      <c r="E10" s="3">
         <v>883400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>963300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>902500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>896800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>880000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>903200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>877100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>860000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>790600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>797200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>791200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>763600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>726700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>742600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>743300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>756300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>736700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>622200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>617600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>612700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>574100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>629000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>592100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>588500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>551400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>621300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>560900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>553300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>505500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>548100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1128,8 +1141,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1226,8 +1240,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1324,41 +1341,44 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>1800</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>2600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7900</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1366,37 +1386,37 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>2800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>15100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1422,8 +1442,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1520,8 +1543,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1553,204 +1579,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5001700</v>
+      </c>
+      <c r="E17" s="3">
         <v>4757800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5143300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4727200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4763300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4536400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4739400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4593600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4900900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4346100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4200700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4093900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4013400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3742600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3801900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3544100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3791800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3653900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3392300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3130500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3247100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3072500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3307000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3131300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3268400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2997100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3463300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3003700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3092700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2974600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3166900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2933100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>203700</v>
+      </c>
+      <c r="E18" s="3">
         <v>160700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>214000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>197500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>200200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>186700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>190200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>191700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>202900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>150300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>157100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>170200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>163800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>125600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>144700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>187600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>162300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>143700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>80000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>98900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>98700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>70600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>109900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>90400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>38700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>64600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>92700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>80500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>74800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-27800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>62900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1785,8 +1818,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1818,25 +1852,25 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5600</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-500</v>
       </c>
       <c r="T20" s="3">
         <v>-500</v>
@@ -1845,13 +1879,13 @@
         <v>-500</v>
       </c>
       <c r="V20" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="W20" s="3">
         <v>-600</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
@@ -1883,400 +1917,415 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>268800</v>
+      </c>
+      <c r="E21" s="3">
         <v>224200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>275300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>255000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>255100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>241000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>241900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>243800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>252900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>197400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>202500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>216500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>205700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>164900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>185700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>224100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>203100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>184100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>119600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>137500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>137100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>109400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>149700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>130300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>79800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>106000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>133400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>121700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>116000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>13300</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E22" s="3">
         <v>14000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>12400</v>
       </c>
       <c r="N22" s="3">
         <v>12400</v>
       </c>
       <c r="O22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="P22" s="3">
         <v>12900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>13600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>17500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>21300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>25000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>26200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>27800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>26700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>33000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>59600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>45200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>46500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>42300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>43800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>64100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>35400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>35500</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>190900</v>
+      </c>
+      <c r="E23" s="3">
         <v>146800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>198400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>181400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>184000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>172100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>176500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>179500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>192000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>142500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>145300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>158300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>147400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>107000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>128800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>164500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>142900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>121900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>55900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>73200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>72000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>42900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>83100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>57300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-20900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>19400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>46200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>38200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>31000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-91900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>27500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E24" s="3">
         <v>35800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>52600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>50900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>52700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>56100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>47100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>48100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>51000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>30000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>37700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>31700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>36400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>25400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>32900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>41600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>36200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>26200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>18000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>17700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>19400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>10200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>15300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>11100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-33100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>10800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2373,204 +2422,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E26" s="3">
         <v>111000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>145900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>130500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>131300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>116000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>129400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>131400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>141000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>112500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>107600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>126600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>111000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>81600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>95900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>122900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>106700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>95700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>42200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>55200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>54300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>36100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>63700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>52200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>14300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>36000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>22900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>19800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-58800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>16700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E27" s="3">
         <v>111000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>145900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>130500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>131300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>116000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>129400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>131400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>141000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>112500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>107600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>126600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>111000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>81600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>95900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>122900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>106700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>95700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>42200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>55200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>54300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>36100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>63700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>52200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>14300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>36000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>22900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>19800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-58800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>16700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2667,13 +2725,16 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2685,17 +2746,17 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-1500</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
@@ -2703,11 +2764,11 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-100</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
@@ -2715,43 +2776,43 @@
         <v>0</v>
       </c>
       <c r="R29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S29" s="3">
         <v>-100</v>
       </c>
       <c r="T29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-400</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-100</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>2300</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>30700</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>-100</v>
       </c>
       <c r="AE29" s="3">
         <v>-100</v>
@@ -2765,8 +2826,11 @@
       <c r="AH29" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2863,8 +2927,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2961,8 +3028,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2994,25 +3064,25 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5600</v>
-      </c>
-      <c r="S32" s="3">
-        <v>500</v>
       </c>
       <c r="T32" s="3">
         <v>500</v>
@@ -3021,13 +3091,13 @@
         <v>500</v>
       </c>
       <c r="V32" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W32" s="3">
         <v>600</v>
       </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
@@ -3059,106 +3129,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E33" s="3">
         <v>111000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>145900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>130500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>131300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>116100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>129800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>129900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>141000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>112500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>107600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>126500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>111000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>81600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>95900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>122800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>106600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>95700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>41800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>55100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>54500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>35800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>64300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>54400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>14100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>66700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>22800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>19700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-58900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>16600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3255,209 +3331,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E35" s="3">
         <v>111000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>145900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>130500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>131300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>116100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>129800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>129900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>141000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>112500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>107600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>126500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>111000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>81600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>95900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>122800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>106600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>95700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>41800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>55100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>54500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>35800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>64300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>54400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>14100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>66700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>22800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>19700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-58900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>16600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E38" s="2">
         <v>45416</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45325</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45227</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45136</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45045</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44954</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44863</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44772</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44590</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44499</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44317</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44226</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44044</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43953</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43862</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43771</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43680</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43589</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43498</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43407</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43316</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43225</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43134</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43036</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42945</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42854</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42763</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3492,8 +3577,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3528,89 +3614,90 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E41" s="3">
         <v>35100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>34600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>163700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>38000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>45400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>84700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>42400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>63000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>43500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>46100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>168800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>132900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>30200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>30000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>29100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>29900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>27100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>31500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>31300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>30500</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3626,8 +3713,11 @@
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3724,89 +3814,92 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>248500</v>
+      </c>
+      <c r="E43" s="3">
         <v>225200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>234800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>224500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>200300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>217900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>239700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>252000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>204500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>210400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>174000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>200300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>169100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>198000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>172700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>188400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>170600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>193900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>206400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>186000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>162300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>180400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>194300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>179100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>165300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>168700</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3822,89 +3915,92 @@
       <c r="AH43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1546200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1533300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1454800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1661900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1540500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1532000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1378600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1504400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1376500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1462100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1242900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1255700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1033600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1120300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1205700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1264300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1005300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1024900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1081500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1271200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1026500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1085600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1052300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1245100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1005000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1055200</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3920,89 +4016,92 @@
       <c r="AH44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E45" s="3">
         <v>85000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>68400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>80600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>76300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>69000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>51000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>72300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>57800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>58800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>54700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>58600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>46400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>54300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>48600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>97100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>64100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>46600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>42000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>55300</v>
-      </c>
-      <c r="W45" s="3">
-        <v>47400</v>
       </c>
       <c r="X45" s="3">
         <v>47400</v>
       </c>
       <c r="Y45" s="3">
+        <v>47400</v>
+      </c>
+      <c r="Z45" s="3">
         <v>63500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>104300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>107300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>83000</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4018,89 +4117,92 @@
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1915100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1878700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1794000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2000500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1843300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1842300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1703200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1863300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1802500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1769300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1517100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1599300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1291600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1435500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1470600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1596000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1408800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1398400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1360000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1542400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1265300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1343200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1337200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1560000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1309000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1337500</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4116,8 +4218,11 @@
       <c r="AH46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4214,89 +4319,92 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3848100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3780200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3719300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3670600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3593700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3489400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3480000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3459700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3424700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3167400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3074300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3032200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2980200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2934900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2856600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2804000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2799400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2841200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2820300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2843300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2791600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2784500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>748800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>745900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>747700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>749700</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4312,89 +4420,92 @@
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1113200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1114800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1116400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1118400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1120400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1122400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1124300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1126600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1128900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1046500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1048800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1051400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1054000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1056600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1059300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1062200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1065200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1068200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1071100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1074500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1077900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1081200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1125000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1130800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1136700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1142800</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4410,8 +4521,11 @@
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4508,8 +4622,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4606,89 +4723,92 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>53500</v>
+      </c>
+      <c r="E52" s="3">
         <v>51000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>47900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>47800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>46500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>42400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>26800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>27400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>21800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>22100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>25100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>20100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>20700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>20400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>18400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>17400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17800</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>28300</v>
       </c>
       <c r="Z52" s="3">
         <v>28300</v>
       </c>
       <c r="AA52" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AB52" s="3">
         <v>27400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>31400</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4704,8 +4824,11 @@
       <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4802,89 +4925,92 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6929900</v>
+      </c>
+      <c r="E54" s="3">
         <v>6824700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6677600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6837200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6603900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6494500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6350000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6478900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6387200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6010000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5668900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5710200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5347600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5449200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5411500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5482300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5294000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5328100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5269800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5478100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5152100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5226700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3239300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3465000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3220900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3261300</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4900,8 +5026,11 @@
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4936,8 +5065,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4972,89 +5102,90 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1285700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1264900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1183300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1319000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1226500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1281700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1195700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1363700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1243300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1267100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1112800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1235800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1029700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1023100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>988100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1176100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1004700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>990400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>786400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>973300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>798500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>820500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>816900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>976500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>783100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>799500</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5070,41 +5201,44 @@
       <c r="AH57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E58" s="3">
         <v>270000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>319000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>434000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>411000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>405000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>295000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>350000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>80000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5112,47 +5246,47 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>210000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>260000</v>
       </c>
       <c r="R58" s="3">
         <v>260000</v>
       </c>
       <c r="S58" s="3">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>15400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>343400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>449400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>195400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>246400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>254400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>389400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>62300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>179300</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5168,89 +5302,92 @@
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1021000</v>
+      </c>
+      <c r="E59" s="3">
         <v>991000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>965800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>986100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>953700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>937700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>944600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>941200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>890900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>862000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>889700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>868300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>809500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>802800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>783100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>774300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>759500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>714400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>671600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>629100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>617200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>607000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>506400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>487900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>475600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>461200</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5266,89 +5403,92 @@
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2523800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2525800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2468000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2739100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2591100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2619300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2545300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2600000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2484100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2209100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2002500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2104100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1839200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2035900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2031200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2210400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1764200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1720200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1801400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2051800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1611100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1673900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1577700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1853800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1321000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1440000</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5364,89 +5504,92 @@
       <c r="AH60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>398600</v>
+      </c>
+      <c r="E61" s="3">
         <v>398500</v>
-      </c>
-      <c r="E61" s="3">
-        <v>398400</v>
       </c>
       <c r="F61" s="3">
         <v>398400</v>
       </c>
       <c r="G61" s="3">
+        <v>398400</v>
+      </c>
+      <c r="H61" s="3">
         <v>448100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>448000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>447900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>600100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>699400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>749000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>748600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>748100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>747700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>747300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>846200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>845700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1202200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1334800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1337300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1339700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1540600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1543500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1546500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1549400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1894100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2508000</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5462,89 +5605,92 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2352700</v>
+      </c>
+      <c r="E62" s="3">
         <v>2373000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2352300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2346100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2333300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2295400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2309900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2335900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2350100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2330600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2269700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2290300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2272300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2252400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2214800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2208800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2208500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2240600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2185400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2191100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2165000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2157600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>317200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>318400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>323700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>324700</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5560,8 +5706,11 @@
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5658,8 +5807,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5756,8 +5908,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5854,89 +6009,92 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5275000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5297300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5218800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5483500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5372600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5362800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5303100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5536000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5533700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5288700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5020800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5142500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4859200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5035700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5092200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5264900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5174900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5295600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5324100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5582600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5316700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5375000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3441400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3721600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3538700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4272700</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5952,8 +6110,11 @@
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5988,8 +6149,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6086,8 +6248,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6184,8 +6349,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6282,8 +6450,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6380,89 +6551,92 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1424200</v>
+      </c>
+      <c r="E72" s="3">
         <v>1279300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1168200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1022400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>891900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>760600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>644500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>514700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>384800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>243800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>131300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>23700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-102800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-213800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-295300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-391200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-514000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-620600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-716400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-758100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-813200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-867700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-915100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-979400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1033900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1028200</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6478,8 +6652,11 @@
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6576,8 +6753,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6674,8 +6854,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6772,89 +6955,92 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1654900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1527400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1458900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1353700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1231300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1131700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1046800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>942900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>853600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>721300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>648100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>567700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>488400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>413500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>319300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>217400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>119100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>32500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-54300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-104500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-164600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-148300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-202100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-256600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-317900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-1011400</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6870,8 +7056,11 @@
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6968,209 +7157,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45507</v>
+      </c>
+      <c r="E80" s="2">
         <v>45416</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45325</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45227</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45136</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45045</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44954</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44863</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44772</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44590</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44499</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44317</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44226</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44044</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43953</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43862</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43771</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43680</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43589</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43498</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43407</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43316</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43225</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43134</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43036</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42945</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42854</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42763</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E81" s="3">
         <v>111000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>145900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>130500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>131300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>116100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>129800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>129900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>141000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>112500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>107600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>126500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>111000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>81600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>95900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>122800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>106600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>95700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>41800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>55100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>54500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>35800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>64300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>54400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>14100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>66700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>22800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>19700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-58900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>16600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7205,106 +7403,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E83" s="3">
         <v>63400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>61300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>57400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>54800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>54200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>51700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>52200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>50000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>47100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>44900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>44400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>43100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>42200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>41300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>40800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>40100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>39200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>39000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>38700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>39800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>39900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>41100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>41400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>40700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>41100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>41200</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7401,8 +7603,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7499,8 +7704,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7597,8 +7805,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7695,8 +7906,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7793,106 +8007,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>221400</v>
+      </c>
+      <c r="E89" s="3">
         <v>200800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>274400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>175000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>150400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>119100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>175300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>169800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>398700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>44300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>98500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>173900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>310300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>249000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>66600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>68300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>263800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>469900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>133600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>170200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>44900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>176200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>47700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>137900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>65400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>109700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>46400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>119100</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7927,106 +8147,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-133900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-105700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-119100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-133700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-122200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-92100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-103500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-102800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-101000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-90500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-101100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-74700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-73100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-74700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-65500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-69800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-47800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-35200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-52500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-56100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-51800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-36500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-42600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-51300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-21800</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8123,8 +8347,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8221,106 +8448,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-133900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-105700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-119100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-127400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-116200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-92100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-87300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-94400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-474800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-90500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-101100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-74700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-70700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-58100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-65500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-48000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-43700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-35200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-30900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-56100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-51800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-36500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-42600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-33500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-42100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-51300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8355,8 +8588,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8439,22 +8673,25 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-100</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8551,8 +8788,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8649,8 +8889,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8747,106 +8990,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-96100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-152700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-40300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-31400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-37600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-88700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-204500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>201800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>38700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-36600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-56900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-260200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-171500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-143000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-184200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-332000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-102500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>50600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-119200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-138000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-103500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-27700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-96100</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8943,102 +9192,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-129000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>125700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-39300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>42300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-20500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>19400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-122700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>35900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>102700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1200</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -656,457 +656,469 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E7" s="2">
         <v>45507</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45416</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45325</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45136</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45045</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44954</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44863</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44772</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44590</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44499</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44317</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44226</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44044</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43953</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43862</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43771</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43680</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43589</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43498</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43407</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43316</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43225</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43134</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43036</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42945</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42854</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42763</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5099400</v>
+      </c>
+      <c r="E8" s="3">
         <v>5205400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4918500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5357300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4924700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4963500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4723100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4929600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4785300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5103800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4496400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4357800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4264100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4177200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3868200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3946600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3731700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3954100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3797600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3472300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3229400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3345800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3143100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3416900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3221700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3307100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3061700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3556000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3084200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3167500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2946800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3229800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2986200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4123900</v>
+      </c>
+      <c r="E9" s="3">
         <v>4248800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4035100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4394000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4022200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4066700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3843200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4026400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3908200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4243800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3705800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3560600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3472900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3413600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3141500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3204000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2988400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3197800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3060900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2850100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2611800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2733100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2569000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2787900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2629600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2718600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2510300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2934700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2523300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2614200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2441300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2681700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2456200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>975500</v>
+      </c>
+      <c r="E10" s="3">
         <v>956600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>883400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>963300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>902500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>896800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>880000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>903200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>877100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>860000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>790600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>797200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>791200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>763600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>726700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>742600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>743300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>756300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>736700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>622200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>617600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>612700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>574100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>629000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>592100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>588500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>551400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>621300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>560900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>553300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>505500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>548100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1243,8 +1256,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1344,44 +1360,47 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1900</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="G14" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+        <v>15800</v>
+      </c>
+      <c r="H14" s="3">
+        <v>5200</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>2600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7900</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1389,37 +1408,37 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>2800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>15100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1445,31 +1464,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>65700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>65100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>63400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>61300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>57400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>54800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>54200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1546,8 +1568,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,210 +1605,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5001700</v>
+        <v>4867900</v>
       </c>
       <c r="E17" s="3">
-        <v>4757800</v>
+        <v>4999800</v>
       </c>
       <c r="F17" s="3">
-        <v>5143300</v>
+        <v>4754500</v>
       </c>
       <c r="G17" s="3">
-        <v>4727200</v>
+        <v>5129300</v>
       </c>
       <c r="H17" s="3">
-        <v>4763300</v>
+        <v>4720100</v>
       </c>
       <c r="I17" s="3">
+        <v>4760100</v>
+      </c>
+      <c r="J17" s="3">
         <v>4536400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4739400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4593600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4900900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4346100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4200700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4093900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4013400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3742600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3801900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3544100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3791800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3653900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3392300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3130500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3247100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3072500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3307000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3131300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3268400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2997100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3463300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3003700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3092700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2974600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3166900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2933100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>203700</v>
+        <v>231500</v>
       </c>
       <c r="E18" s="3">
-        <v>160700</v>
+        <v>205600</v>
       </c>
       <c r="F18" s="3">
-        <v>214000</v>
+        <v>164100</v>
       </c>
       <c r="G18" s="3">
-        <v>197500</v>
+        <v>227900</v>
       </c>
       <c r="H18" s="3">
-        <v>200200</v>
+        <v>204600</v>
       </c>
       <c r="I18" s="3">
-        <v>186700</v>
+        <v>203500</v>
       </c>
       <c r="J18" s="3">
+        <v>186800</v>
+      </c>
+      <c r="K18" s="3">
         <v>190200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>191700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>202900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>150300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>157100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>170200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>163800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>125600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>144700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>187600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>162300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>143700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>80000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>98900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>98700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>70600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>109900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>90400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>38700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>64600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>92700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>80500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>74800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-27800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>62900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1819,31 +1851,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+        <v>-700</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1855,25 +1888,25 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5600</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-500</v>
       </c>
       <c r="U20" s="3">
         <v>-500</v>
@@ -1882,13 +1915,13 @@
         <v>-500</v>
       </c>
       <c r="W20" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="X20" s="3">
         <v>-600</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
@@ -1920,412 +1953,427 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>268800</v>
+        <v>297200</v>
       </c>
       <c r="E21" s="3">
-        <v>224200</v>
+        <v>270700</v>
       </c>
       <c r="F21" s="3">
-        <v>275300</v>
+        <v>227500</v>
       </c>
       <c r="G21" s="3">
-        <v>255000</v>
+        <v>289900</v>
       </c>
       <c r="H21" s="3">
-        <v>255100</v>
+        <v>262000</v>
       </c>
       <c r="I21" s="3">
+        <v>258300</v>
+      </c>
+      <c r="J21" s="3">
         <v>241000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>241900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>243800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>252900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>197400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>202500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>216500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>205700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>164900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>185700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>224100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>203100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>184100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>119600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>137500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>137100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>109400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>149700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>130300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>79800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>106000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>133400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>121700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>116000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>13300</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E22" s="3">
         <v>12800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14000</v>
       </c>
-      <c r="F22" s="3">
-        <v>15600</v>
-      </c>
       <c r="G22" s="3">
-        <v>16200</v>
+        <v>13200</v>
       </c>
       <c r="H22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="I22" s="3">
         <v>16300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7800</v>
-      </c>
-      <c r="N22" s="3">
-        <v>12400</v>
       </c>
       <c r="O22" s="3">
         <v>12400</v>
       </c>
       <c r="P22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="Q22" s="3">
         <v>12900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>17500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>25000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>26200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>27800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>26700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>33000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>59600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>45200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>46500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>42300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>43800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>64100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>35400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>35500</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E23" s="3">
         <v>190900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>146800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>198400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>181400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>184000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>172100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>176500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>179500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>192000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>142500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>145300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>158300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>147400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>107000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>128800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>164500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>142900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>121900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>55900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>73200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>72000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>42900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>83100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>57300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-20900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>19400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>46200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>38200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>31000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-91900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>27500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E24" s="3">
         <v>45900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>35800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>52600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>50900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>52700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>56100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>47100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>48100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>51000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>30000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>37700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>31700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>36400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>25400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>32900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>41600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>36200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>26200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>13700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>18000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>17700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>19400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>10200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>15300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>11100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-33100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>10800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2425,210 +2473,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E26" s="3">
         <v>145000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>111000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>145900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>130500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>131300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>116000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>129400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>131400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>141000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>112500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>107600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>126600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>111000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>81600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>95900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>122900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>106700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>95700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>42200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>55200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>54300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>36100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>63700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>52200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>14300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>36000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>22900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>19800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-58800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>16700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E27" s="3">
         <v>145000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>111000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>145900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>130500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>131300</v>
       </c>
-      <c r="I27" s="3">
-        <v>116000</v>
-      </c>
       <c r="J27" s="3">
+        <v>116100</v>
+      </c>
+      <c r="K27" s="3">
         <v>129400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>131400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>141000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>112500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>107600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>126600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>111000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>81600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>95900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>122900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>106700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>95700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>42200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>55200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>54300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>36100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>63700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>52200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>14300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>36000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>22900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>19800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-58800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>16700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2728,13 +2785,16 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2749,17 +2809,17 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-1500</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -2767,11 +2827,11 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-100</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
@@ -2779,43 +2839,43 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T29" s="3">
         <v>-100</v>
       </c>
       <c r="U29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-300</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>2300</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>30700</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>-100</v>
       </c>
       <c r="AF29" s="3">
         <v>-100</v>
@@ -2829,8 +2889,11 @@
       <c r="AI29" s="3">
         <v>-100</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2930,8 +2993,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3031,31 +3097,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3067,25 +3136,25 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5600</v>
-      </c>
-      <c r="T32" s="3">
-        <v>500</v>
       </c>
       <c r="U32" s="3">
         <v>500</v>
@@ -3094,13 +3163,13 @@
         <v>500</v>
       </c>
       <c r="W32" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="X32" s="3">
         <v>600</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
@@ -3132,109 +3201,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E33" s="3">
         <v>145000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>111000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>145900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>130500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>131300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>116100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>129800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>129900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>141000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>112500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>107600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>126500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>111000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>81600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>95900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>122800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>106600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>95700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>41800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>55100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>54500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>35800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>64300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>54400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>14100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>66700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>22800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>19700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-58900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>16600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3334,215 +3409,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E35" s="3">
         <v>145000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>111000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>145900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>130500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>131300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>116100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>129800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>129900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>141000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>112500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>107600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>126500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>111000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>81600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>95900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>122800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>106600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>95700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>41800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>55100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>54500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>35800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>64300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>54400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>14100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>66700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>22800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>19700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-58900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>16600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E38" s="2">
         <v>45507</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45416</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45325</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45136</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45045</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44954</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44863</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44772</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44590</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44499</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44317</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44226</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44044</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43953</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43862</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43771</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43680</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43589</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43498</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43407</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43316</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43225</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43134</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43036</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42945</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42854</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42763</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3578,8 +3662,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3615,92 +3700,93 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E41" s="3">
         <v>38100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>33900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>34600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>163700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>38000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>45400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>42400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>63000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>43500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>46100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>168800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>132900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>30200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>30000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>29100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>29900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>27100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>31500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>31300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>30500</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3716,8 +3802,11 @@
       <c r="AI41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3817,92 +3906,95 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>266700</v>
+      </c>
+      <c r="E43" s="3">
         <v>248500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>225200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>234800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>224500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>200300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>217900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>239700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>252000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>204500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>210400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>174000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>200300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>169100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>198000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>172700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>188400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>170600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>193900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>206400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>186000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>162300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>180400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>194300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>179100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>165300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>168700</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3918,92 +4010,95 @@
       <c r="AI43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1720000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1546200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1533300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1454800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1661900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1540500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1532000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1378600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1504400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1376500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1462100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1242900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1255700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1033600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1120300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1205700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1264300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1005300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1024900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1081500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1271200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1026500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1085600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1052300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1245100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1005000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1055200</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4019,92 +4114,95 @@
       <c r="AI44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>82300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>85000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>68400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>80600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>76300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>69000</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>51000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>72300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>57800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>58800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>54700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>58600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>46400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>54300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>48600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>97100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>64100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>46600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>42000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>55300</v>
-      </c>
-      <c r="X45" s="3">
-        <v>47400</v>
       </c>
       <c r="Y45" s="3">
         <v>47400</v>
       </c>
       <c r="Z45" s="3">
+        <v>47400</v>
+      </c>
+      <c r="AA45" s="3">
         <v>63500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>104300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>107300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>83000</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4120,92 +4218,95 @@
       <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2097100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1915100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1878700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1794000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2000500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1843300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1842300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1703200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1863300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1802500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1769300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1517100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1599300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1291600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1435500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1470600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1596000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1408800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1398400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1360000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1542400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1265300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1343200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1337200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1560000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1309000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1337500</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4221,31 +4322,34 @@
       <c r="AI46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4322,92 +4426,95 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3947000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3848100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3780200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3719300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3670600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3593700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3489400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3480000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3459700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3424700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3167400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3074300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3032200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2980200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2934900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2856600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2804000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2799400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2841200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2820300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2843300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2791600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2784500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>748800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>745900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>747700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>749700</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4423,92 +4530,95 @@
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1111600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1113200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1114800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1116400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1118400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1120400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1122400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1124300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1126600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1128900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1046500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1048800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1051400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1054000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1056600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1059300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1062200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1065200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1068200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1071100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1074500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1077900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1081200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1125000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1130800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1136700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1142800</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4524,8 +4634,11 @@
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4625,8 +4738,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4726,92 +4842,95 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>53500</v>
+        <v>55600</v>
       </c>
       <c r="E52" s="3">
-        <v>51000</v>
+        <v>50000</v>
       </c>
       <c r="F52" s="3">
-        <v>47900</v>
+        <v>48400</v>
       </c>
       <c r="G52" s="3">
-        <v>47800</v>
+        <v>43800</v>
       </c>
       <c r="H52" s="3">
-        <v>46500</v>
+        <v>40300</v>
       </c>
       <c r="I52" s="3">
-        <v>40400</v>
+        <v>38600</v>
       </c>
       <c r="J52" s="3">
+        <v>33700</v>
+      </c>
+      <c r="K52" s="3">
         <v>42400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>26800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>27400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>22100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>25100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>20100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>20700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>20400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>18400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>17900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>17800</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>28300</v>
       </c>
       <c r="AA52" s="3">
         <v>28300</v>
       </c>
       <c r="AB52" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AC52" s="3">
         <v>27400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>31400</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4827,8 +4946,11 @@
       <c r="AI52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4928,92 +5050,95 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7216200</v>
+      </c>
+      <c r="E54" s="3">
         <v>6929900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6824700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6677600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6837200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6603900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6494500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6350000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6478900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6387200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6010000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5668900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5710200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5347600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5449200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5411500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5482300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5294000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5328100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5269800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5478100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5152100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5226700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3239300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3465000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3220900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3261300</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5029,8 +5154,11 @@
       <c r="AI54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5066,8 +5194,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5103,92 +5232,93 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1420400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1285700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1264900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1183300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1319000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1226500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1281700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1195700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1363700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1243300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1267100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1112800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1235800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1029700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1023100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>988100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1176100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1004700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>990400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>786400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>973300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>798500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>820500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>816900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>976500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>783100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>799500</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5204,44 +5334,47 @@
       <c r="AI57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>217000</v>
+        <v>408300</v>
       </c>
       <c r="E58" s="3">
-        <v>270000</v>
+        <v>379800</v>
       </c>
       <c r="F58" s="3">
-        <v>319000</v>
+        <v>426900</v>
       </c>
       <c r="G58" s="3">
-        <v>434000</v>
+        <v>479700</v>
       </c>
       <c r="H58" s="3">
-        <v>411000</v>
+        <v>614500</v>
       </c>
       <c r="I58" s="3">
-        <v>400000</v>
+        <v>590400</v>
       </c>
       <c r="J58" s="3">
+        <v>578900</v>
+      </c>
+      <c r="K58" s="3">
         <v>405000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>295000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>350000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>80000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -5249,47 +5382,47 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>210000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>260000</v>
       </c>
       <c r="S58" s="3">
         <v>260000</v>
       </c>
       <c r="T58" s="3">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>15400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>343400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>449400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>195400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>246400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>254400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>389400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>62300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>179300</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5305,92 +5438,95 @@
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1021000</v>
+        <v>327500</v>
       </c>
       <c r="E59" s="3">
-        <v>991000</v>
+        <v>328300</v>
       </c>
       <c r="F59" s="3">
-        <v>965800</v>
+        <v>316600</v>
       </c>
       <c r="G59" s="3">
-        <v>986100</v>
+        <v>572200</v>
       </c>
       <c r="H59" s="3">
-        <v>953700</v>
+        <v>263800</v>
       </c>
       <c r="I59" s="3">
-        <v>937700</v>
-      </c>
-      <c r="J59" s="3">
+        <v>246600</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>944600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>941200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>890900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>862000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>889700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>868300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>809500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>802800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>783100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>774300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>759500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>714400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>671600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>629100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>617200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>607000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>506400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>487900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>475600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>461200</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5406,92 +5542,95 @@
       <c r="AI59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2742000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2523800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2525800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2468000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2739100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2591100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2619300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2545300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2600000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2484100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2209100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2002500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2104100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1839200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2035900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2031200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2210400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1764200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1720200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1801400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2051800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1611100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1673900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1577700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1853800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1321000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1440000</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5507,92 +5646,95 @@
       <c r="AI60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>398600</v>
+        <v>2423400</v>
       </c>
       <c r="E61" s="3">
-        <v>398500</v>
+        <v>2456700</v>
       </c>
       <c r="F61" s="3">
-        <v>398400</v>
+        <v>2468100</v>
       </c>
       <c r="G61" s="3">
-        <v>398400</v>
+        <v>2511800</v>
       </c>
       <c r="H61" s="3">
-        <v>448100</v>
+        <v>2483100</v>
       </c>
       <c r="I61" s="3">
-        <v>448000</v>
+        <v>2523200</v>
       </c>
       <c r="J61" s="3">
+        <v>2485800</v>
+      </c>
+      <c r="K61" s="3">
         <v>447900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>600100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>699400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>749000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>748600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>748100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>747700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>747300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>846200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>845700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1202200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1334800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1337300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1339700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1540600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1543500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1546500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1549400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1894100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2508000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
@@ -5608,92 +5750,95 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2352700</v>
+        <v>219100</v>
       </c>
       <c r="E62" s="3">
-        <v>2373000</v>
+        <v>218900</v>
       </c>
       <c r="F62" s="3">
-        <v>2352300</v>
+        <v>222700</v>
       </c>
       <c r="G62" s="3">
-        <v>2346100</v>
+        <v>143500</v>
       </c>
       <c r="H62" s="3">
-        <v>2333300</v>
+        <v>189100</v>
       </c>
       <c r="I62" s="3">
-        <v>2295400</v>
+        <v>194200</v>
       </c>
       <c r="J62" s="3">
+        <v>190900</v>
+      </c>
+      <c r="K62" s="3">
         <v>2309900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2335900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2350100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2330600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2269700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2290300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2272300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2252400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2214800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2208800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2208500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2240600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2185400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2191100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2165000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2157600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>317200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>318400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>323700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>324700</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5709,8 +5854,11 @@
       <c r="AI62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5810,8 +5958,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5911,8 +6062,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6012,92 +6166,95 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5454100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5275000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5297300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5218800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5483500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5372600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5362800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5303100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5536000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5533700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5288700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5020800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5142500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4859200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5035700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5092200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5264900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5174900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5295600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5324100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5582600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5316700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5375000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3441400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3721600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3538700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4272700</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6113,8 +6270,11 @@
       <c r="AI66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6150,8 +6310,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6251,8 +6412,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6352,8 +6516,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6453,8 +6620,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6554,92 +6724,95 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1580000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1424200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1279300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1168200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1022400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>891900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>760600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>644500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>514700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>384800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>243800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>131300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>23700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-102800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-213800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-295300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-391200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-514000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-620600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-716400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-758100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-813200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-867700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-915100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-979400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1033900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1028200</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6655,8 +6828,11 @@
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6756,8 +6932,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6857,8 +7036,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6958,92 +7140,95 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1762200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1654900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1527400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1458900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1353700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1231300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1131700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1046800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>942900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>853600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>721300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>648100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>567700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>488400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>413500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>319300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>217400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>119100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>32500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-54300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-104500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-164600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-148300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-202100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-256600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-317900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-1011400</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7059,8 +7244,11 @@
       <c r="AI76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7160,215 +7348,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45598</v>
+      </c>
+      <c r="E80" s="2">
         <v>45507</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45416</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45325</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45136</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45045</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44954</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44863</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44772</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44590</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44499</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44317</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44226</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44044</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43953</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43862</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43771</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43680</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43589</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43498</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43407</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43316</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43225</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43134</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43036</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42945</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42854</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42763</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E81" s="3">
         <v>145000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>111000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>145900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>130500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>131300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>116100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>129800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>129900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>141000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>112500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>107600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>126500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>111000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>81600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>95900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>122800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>106600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>95700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>41800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>55100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>54500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>35800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>64300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>54400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>14100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>66700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>22800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>19700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-58900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>16600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7404,109 +7601,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>65100</v>
+        <v>57400</v>
       </c>
       <c r="E83" s="3">
-        <v>63400</v>
+        <v>54800</v>
       </c>
       <c r="F83" s="3">
-        <v>61300</v>
+        <v>54200</v>
       </c>
       <c r="G83" s="3">
-        <v>57400</v>
+        <v>42500</v>
       </c>
       <c r="H83" s="3">
-        <v>54800</v>
+        <v>52200</v>
       </c>
       <c r="I83" s="3">
-        <v>54200</v>
+        <v>50000</v>
       </c>
       <c r="J83" s="3">
+        <v>47100</v>
+      </c>
+      <c r="K83" s="3">
         <v>51700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>52200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>50000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>47100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>44900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>45400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>44400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>43100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>42200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>41300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>40800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>40100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>39200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>39000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>38700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>39800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>39900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>41100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>41400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>40700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>41100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>41200</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7606,8 +7807,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7707,8 +7911,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7808,8 +8015,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7909,8 +8119,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8010,109 +8223,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>206800</v>
+      </c>
+      <c r="E89" s="3">
         <v>221400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>200800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>274400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>175000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>150400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>119100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>175300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>169800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>398700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>44300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>98500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>173900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>310300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>249000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>66600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>68300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>263800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>469900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>133600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>170200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>44900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>176200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>47700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>137900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>65400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>109700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>46400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>119100</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI89" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8148,109 +8367,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-187900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-133900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-105700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-119100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-133700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-122200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-92100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-103500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-102800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-101000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-90500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-101100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-74700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-73100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-74700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-65500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-69800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-47800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-35200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-52500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-56100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-51800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-36500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-27700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-51300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-21800</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8350,8 +8573,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8451,109 +8677,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-187900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-133900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-105700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-119100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-127400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-116200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-92100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-87300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-94400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-474800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-90500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-101100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-74700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-70700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-58100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-65500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-48000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-43700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-35200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-30900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-56100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-51800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-36500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-33500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-42100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-51300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8589,31 +8821,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8676,22 +8909,25 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-100</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8791,8 +9027,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8892,8 +9131,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8993,132 +9235,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-84500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-96100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-152700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-40300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-31400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-37600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-88700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-204500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>201800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>38700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-36600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-56900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-260200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-171500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-143000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-184200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-332000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-102500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>50600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-119200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-138000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-103500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-27700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-96100</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9195,105 +9443,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-129000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>125700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-39300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>42300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>19400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-122700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>35900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>102700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1200</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -656,469 +656,482 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E7" s="2">
         <v>45598</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45507</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45416</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45325</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45227</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45136</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45045</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44954</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44863</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44772</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44590</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44499</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44317</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44226</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44044</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43953</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43862</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43771</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43680</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43589</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43498</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43407</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43316</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43225</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43134</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43036</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42945</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42854</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5278500</v>
+      </c>
+      <c r="E8" s="3">
         <v>5099400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5205400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4918500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5357300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4924700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4963500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4723100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4929600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4785300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5103800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4496400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4357800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4264100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4177200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3868200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3946600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3731700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3954100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3797600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3472300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3229400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3345800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3143100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3416900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3221700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3307100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3061700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3556000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3084200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3167500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2946800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3229800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2986200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4329500</v>
+      </c>
+      <c r="E9" s="3">
         <v>4123900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4248800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4035100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4394000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4022200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4066700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3843200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4026400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3908200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4243800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3705800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3560600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3472900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3413600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3141500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3204000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2988400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3197800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3060900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2850100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2611800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2733100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2569000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2787900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2629600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2718600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2510300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2934700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2523300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2614200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2441300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2681700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2456200</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>949000</v>
+      </c>
+      <c r="E10" s="3">
         <v>975500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>956600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>883400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>963300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>902500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>896800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>880000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>903200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>877100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>860000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>790600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>797200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>791200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>763600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>726700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>742600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>743300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>756300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>736700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>622200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>617600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>612700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>574100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>629000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>592100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>588500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>551400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>621300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>560900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>553300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>505500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>548100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,8 +1168,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1259,8 +1273,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1363,47 +1380,50 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3300</v>
       </c>
-      <c r="G14" s="3">
-        <v>15800</v>
-      </c>
       <c r="H14" s="3">
+        <v>7300</v>
+      </c>
+      <c r="I14" s="3">
         <v>5200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>2600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7900</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1411,37 +1431,37 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>2800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>15100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1467,35 +1487,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E15" s="3">
         <v>65700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>65100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>63400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>61300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>57400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>54800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>54200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1571,8 +1594,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,216 +1632,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5099000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4867900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4999800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4754500</v>
       </c>
-      <c r="G17" s="3">
-        <v>5129300</v>
-      </c>
       <c r="H17" s="3">
+        <v>5137800</v>
+      </c>
+      <c r="I17" s="3">
         <v>4720100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4760100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4536400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4739400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4593600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4900900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4346100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4200700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4093900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4013400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3742600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3801900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3544100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3791800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3653900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3392300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3130500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3247100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3072500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3307000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3131300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3268400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2997100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3463300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3003700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3092700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2974600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3166900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2933100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>179500</v>
+      </c>
+      <c r="E18" s="3">
         <v>231500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>205600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>164100</v>
       </c>
-      <c r="G18" s="3">
-        <v>227900</v>
-      </c>
       <c r="H18" s="3">
+        <v>219500</v>
+      </c>
+      <c r="I18" s="3">
         <v>204600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>203500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>186800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>190200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>191700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>202900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>150300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>157100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>170200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>163800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>125600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>144700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>187600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>162300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>143700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>80000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>98900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>98700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>70600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>109900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>90400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>38700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>64600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>92700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>80500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>74800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-27800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>62900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1852,8 +1885,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1866,8 +1900,8 @@
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3">
-        <v>-700</v>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>8</v>
@@ -1878,8 +1912,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1891,25 +1925,25 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5600</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-500</v>
       </c>
       <c r="V20" s="3">
         <v>-500</v>
@@ -1918,13 +1952,13 @@
         <v>-500</v>
       </c>
       <c r="X20" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="Y20" s="3">
         <v>-600</v>
       </c>
       <c r="Z20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
@@ -1956,424 +1990,439 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>247400</v>
+      </c>
+      <c r="E21" s="3">
         <v>297200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>270700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>227500</v>
       </c>
-      <c r="G21" s="3">
-        <v>289900</v>
-      </c>
       <c r="H21" s="3">
+        <v>280800</v>
+      </c>
+      <c r="I21" s="3">
         <v>262000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>258300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>241000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>241900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>243800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>252900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>197400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>202500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>216500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>205700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>164900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>185700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>224100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>203100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>184100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>119600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>137500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>137100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>109400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>149700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>130300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>79800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>106000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>133400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>121700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>116000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>13300</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E22" s="3">
         <v>12600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14000</v>
       </c>
-      <c r="G22" s="3">
-        <v>13200</v>
-      </c>
       <c r="H22" s="3">
+        <v>13400</v>
+      </c>
+      <c r="I22" s="3">
         <v>18000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7800</v>
-      </c>
-      <c r="O22" s="3">
-        <v>12400</v>
       </c>
       <c r="P22" s="3">
         <v>12400</v>
       </c>
       <c r="Q22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="R22" s="3">
         <v>12900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>13800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>17500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>18900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>25000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>26200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>27800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>26700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>33000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>59600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>45200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>46500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>42300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>43800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>64100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>35400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>35500</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>166300</v>
+      </c>
+      <c r="E23" s="3">
         <v>216800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>190900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>146800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>198400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>181400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>184000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>172100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>176500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>179500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>192000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>142500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>145300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>158300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>147400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>107000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>128800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>164500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>142900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>121900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>55900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>73200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>72000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>42900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>83100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>57300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-20900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>19400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>46200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>38200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>31000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-91900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>27500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E24" s="3">
         <v>61000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>45900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>35800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>52600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>50900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>52700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>56100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>47100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>48100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>51000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>30000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>37700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>31700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>36400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>25400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>32900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>41600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>36200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>26200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>13700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>18000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>17700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>19400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>10200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>15300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>11100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-33100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2476,216 +2525,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>122700</v>
+      </c>
+      <c r="E26" s="3">
         <v>155700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>145000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>111000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>145900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>130500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>131300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>116000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>129400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>131400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>141000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>112500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>107600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>126600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>111000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>81600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>95900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>122900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>106700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>95700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>42200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>55200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>54300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>36100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>63700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>52200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>14300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>36000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>22900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>19800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-58800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>16700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>122700</v>
+      </c>
+      <c r="E27" s="3">
         <v>155700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>145000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>111000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>145900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>130500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>131300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>116100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>129400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>131400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>141000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>112500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>107600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>126600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>111000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>81600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>95900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>122900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>106700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>95700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>42200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>55200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>54300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>36100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>63700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>52200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>14300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>36000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>22900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>19800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-58800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>16700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2788,8 +2846,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2812,17 +2873,17 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-1500</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -2830,11 +2891,11 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-100</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
@@ -2842,43 +2903,43 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U29" s="3">
         <v>-100</v>
       </c>
       <c r="V29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-400</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-100</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-300</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>2300</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>30700</v>
-      </c>
-      <c r="AF29" s="3">
-        <v>-100</v>
       </c>
       <c r="AG29" s="3">
         <v>-100</v>
@@ -2892,8 +2953,11 @@
       <c r="AJ29" s="3">
         <v>-100</v>
       </c>
+      <c r="AK29" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2996,8 +3060,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3100,8 +3167,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3114,8 +3184,8 @@
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3">
-        <v>700</v>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>8</v>
@@ -3126,8 +3196,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3139,25 +3209,25 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5600</v>
-      </c>
-      <c r="U32" s="3">
-        <v>500</v>
       </c>
       <c r="V32" s="3">
         <v>500</v>
@@ -3166,13 +3236,13 @@
         <v>500</v>
       </c>
       <c r="X32" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Y32" s="3">
         <v>600</v>
       </c>
       <c r="Z32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
@@ -3204,112 +3274,118 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>122700</v>
+      </c>
+      <c r="E33" s="3">
         <v>155700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>145000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>111000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>145900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>130500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>131300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>116100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>129800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>129900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>141000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>112500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>107600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>126500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>111000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>81600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>95900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>122800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>106600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>95700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>41800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>55100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>54500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>35800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>64300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>54400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>14100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>66700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>22800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>19700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-58900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>16600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3412,221 +3488,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>122700</v>
+      </c>
+      <c r="E35" s="3">
         <v>155700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>145000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>111000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>145900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>130500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>131300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>116100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>129800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>129900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>141000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>112500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>107600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>126500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>111000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>81600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>95900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>122800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>106600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>95700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>41800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>55100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>54500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>35800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>64300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>54400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>14100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>66700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>22800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>19700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-58900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>16600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E38" s="2">
         <v>45598</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45507</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45416</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45325</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45227</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45136</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45045</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44954</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44863</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44772</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44590</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44499</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44317</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44226</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44044</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43953</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43862</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43771</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43680</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43589</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43498</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43407</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43316</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43225</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43134</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43036</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42945</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42854</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3663,8 +3748,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3701,95 +3787,96 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E41" s="3">
         <v>33900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>38100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>35100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>163700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>38000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>45400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>84700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>42400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>63000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>43500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>46100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>168800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>132900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>30200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>30000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>29100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>29900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>27100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>31500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>31300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>30500</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3805,8 +3892,11 @@
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3909,95 +3999,98 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>277300</v>
+      </c>
+      <c r="E43" s="3">
         <v>266700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>248500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>225200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>234800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>224500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>200300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>217900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>239700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>252000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>204500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>210400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>174000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>200300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>169100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>198000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>172700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>188400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>170600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>193900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>206400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>186000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>162300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>180400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>194300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>179100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>165300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>168700</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4013,95 +4106,98 @@
       <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1509000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1720000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1546200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1533300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1454800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1661900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1540500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1532000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1378600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1504400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1376500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1462100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1242900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1255700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1033600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1120300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1205700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1264300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1005300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1024900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1081500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1271200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1026500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1085600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1052300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1245100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1005000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1055200</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4117,8 +4213,11 @@
       <c r="AJ44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4143,69 +4242,69 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>51000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>72300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>57800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>58800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>54700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>58600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>46400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>54300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>48600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>97100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>64100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>46600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>42000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>55300</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>47400</v>
       </c>
       <c r="Z45" s="3">
         <v>47400</v>
       </c>
       <c r="AA45" s="3">
+        <v>47400</v>
+      </c>
+      <c r="AB45" s="3">
         <v>63500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>104300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>107300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>83000</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4221,95 +4320,98 @@
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1879000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2097100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1915100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1878700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1794000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2000500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1843300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1842300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1703200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1863300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1802500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1769300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1517100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1599300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1291600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1435500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1470600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1596000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1408800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1398400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1360000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1542400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1265300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1343200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1337200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1560000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1309000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1337500</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4325,8 +4427,11 @@
       <c r="AJ46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4351,8 +4456,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4429,95 +4534,98 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3997900</v>
+      </c>
+      <c r="E48" s="3">
         <v>3947000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3848100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3780200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3719300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3670600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3593700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3489400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3480000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3459700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3424700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3167400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3074300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3032200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2980200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2934900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2856600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2804000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2799400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2841200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2820300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2843300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2791600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2784500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>748800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>745900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>747700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>749700</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4533,95 +4641,98 @@
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1109900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1111600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1113200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1114800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1116400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1118400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1120400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1122400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1124300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1126600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1128900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1046500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1048800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1051400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1054000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1056600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1059300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1062200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1065200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1068200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1071100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1074500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1077900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1081200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1125000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1130800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1136700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1142800</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4637,8 +4748,11 @@
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4741,8 +4855,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4845,95 +4962,98 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E52" s="3">
         <v>55600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>50000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>48400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>43800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>38600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>33700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>42400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>26800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>28700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>27400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>21800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>22100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>25100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>20100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>20700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>20400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>18400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>17400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>17800</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>28300</v>
       </c>
       <c r="AB52" s="3">
         <v>28300</v>
       </c>
       <c r="AC52" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AD52" s="3">
         <v>27400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>31400</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4949,8 +5069,11 @@
       <c r="AJ52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5053,95 +5176,98 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7065300</v>
+      </c>
+      <c r="E54" s="3">
         <v>7216200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6929900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6824700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6677600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6837200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6603900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6494500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6350000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6478900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6387200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6010000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5668900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5710200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5347600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5449200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5411500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5482300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5294000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5328100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5269800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5478100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5152100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5226700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3239300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3465000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3220900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3261300</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5157,8 +5283,11 @@
       <c r="AJ54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5195,8 +5324,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5233,95 +5363,96 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1253500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1420400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1285700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1264900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1183300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1319000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1226500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1281700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1195700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1363700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1243300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1267100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1112800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1235800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1029700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1023100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>988100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1176100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1004700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>990400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>786400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>973300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>798500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>820500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>816900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>976500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>783100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>799500</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5337,47 +5468,50 @@
       <c r="AJ57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>375800</v>
+      </c>
+      <c r="E58" s="3">
         <v>408300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>379800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>426900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>479700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>614500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>590400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>578900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>405000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>295000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>350000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>80000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5385,47 +5519,47 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>210000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>260000</v>
       </c>
       <c r="T58" s="3">
         <v>260000</v>
       </c>
       <c r="U58" s="3">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>15400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>343400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>449400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>195400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>246400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>254400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>389400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>62300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>179300</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5441,95 +5575,98 @@
       <c r="AJ58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>616300</v>
+      </c>
+      <c r="E59" s="3">
         <v>327500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>328300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>316600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>572200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>263800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>246600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>944600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>941200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>890900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>862000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>889700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>868300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>809500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>802800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>783100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>774300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>759500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>714400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>671600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>629100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>617200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>607000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>506400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>487900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>475600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>461200</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5545,95 +5682,98 @@
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2534100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2742000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2523800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2525800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2468000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2739100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2591100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2619300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2545300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2600000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2484100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2209100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2002500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2104100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1839200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2035900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2031200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2210400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1764200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1720200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1801400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2051800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1611100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1673900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1577700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1853800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1321000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1440000</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5649,95 +5789,98 @@
       <c r="AJ60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2476400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2423400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2456700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2468100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2511800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2483100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2523200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2485800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>447900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>600100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>699400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>749000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>748600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>748100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>747700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>747300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>846200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>845700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1202200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1334800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1337300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1339700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1540600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1543500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1546500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1549400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1894100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2508000</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5753,95 +5896,98 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>132200</v>
+      </c>
+      <c r="E62" s="3">
         <v>219100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>218900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>222700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>143500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>189100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>194200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>190900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2309900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2335900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2350100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2330600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2269700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2290300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2272300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2252400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2214800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2208800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2208500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2240600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2185400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2191100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2165000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2157600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>317200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>318400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>323700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>324700</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5857,8 +6003,11 @@
       <c r="AJ62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5961,8 +6110,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6065,8 +6217,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6169,95 +6324,98 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5217900</v>
+      </c>
+      <c r="E66" s="3">
         <v>5454100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5275000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5297300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5218800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5483500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5372600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5362800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5303100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5536000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5533700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5288700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5020800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5142500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4859200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5035700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5092200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5264900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5174900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5295600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5324100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5582600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5316700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5375000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3441400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3721600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3538700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4272700</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6273,8 +6431,11 @@
       <c r="AJ66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6311,8 +6472,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6415,8 +6577,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6519,8 +6684,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6623,8 +6791,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6727,95 +6898,98 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1702600</v>
+      </c>
+      <c r="E72" s="3">
         <v>1580000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1424200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1279300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1168200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1022400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>891900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>760600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>644500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>514700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>384800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>243800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>131300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>23700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-102800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-213800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-295300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-391200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-514000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-620600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-716400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-758100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-813200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-867700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-915100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-979400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1033900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1028200</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6831,8 +7005,11 @@
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6935,8 +7112,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7039,8 +7219,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7143,95 +7326,98 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1847500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1762200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1654900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1527400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1458900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1353700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1231300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1131700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1046800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>942900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>853600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>721300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>648100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>567700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>488400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>413500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>319300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>217400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>119100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>32500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-54300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-104500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-164600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-148300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-202100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-256600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-317900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-1011400</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7247,8 +7433,11 @@
       <c r="AJ76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7351,221 +7540,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45689</v>
+      </c>
+      <c r="E80" s="2">
         <v>45598</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45507</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45416</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45325</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45227</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45136</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45045</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44954</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44863</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44772</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44590</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44499</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44317</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44226</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44044</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43953</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43862</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43771</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43680</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43589</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43498</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43407</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43316</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43225</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43134</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43036</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42945</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42854</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>122700</v>
+      </c>
+      <c r="E81" s="3">
         <v>155700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>145000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>111000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>145900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>130500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>131300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>116100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>129800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>129900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>141000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>112500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>107600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>126500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>111000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>81600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>95900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>122800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>106600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>95700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>41800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>55100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>54500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>35800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>64300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>54400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>14100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>66700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>22800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>19700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-58900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>16600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7602,112 +7800,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E83" s="3">
         <v>57400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>54800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>54200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>42500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>52200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>50000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>47100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>51700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>52200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>50000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>47100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>44900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>45800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>45400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>44400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>43100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>42200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>41300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>40800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>40100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>39200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>39000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>38700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>39800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>39900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>41100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>41400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>40700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>41100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>41200</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ83" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7810,8 +8012,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7914,8 +8119,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8018,8 +8226,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8122,8 +8333,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8226,112 +8440,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>271900</v>
+      </c>
+      <c r="E89" s="3">
         <v>206800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>221400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>200800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>274400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>175000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>150400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>119100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>175300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>169800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>398700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>44300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>98500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>173900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>310300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>249000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>66600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>68300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>263800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>469900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>133600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>170200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>44900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>176200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>47700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>137900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>65400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>109700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>46400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>119100</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ89" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8368,112 +8588,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-160400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-187900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-133900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-105700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-119100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-133700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-122200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-92100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-103500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-102800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-101000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-90500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-101100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-74700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-73100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-74700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-65500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-69800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-47800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-35200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-52500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-56100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-51800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-36500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-42600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-27700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-51300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-21800</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ91" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8576,8 +8800,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8680,112 +8907,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-187900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-133900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-105700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-119100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-127400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-116200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-92100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-87300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-94400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-474800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-90500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-101100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-74700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-70700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-58100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-65500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-48000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-43700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-35200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-30900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-56100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-51800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-36500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-33500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-42100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-51300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ94" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8822,13 +9055,14 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3">
+        <v>0</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>8</v>
@@ -8836,11 +9070,11 @@
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
@@ -8848,8 +9082,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8912,22 +9146,25 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-100</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9030,8 +9267,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9134,8 +9374,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9238,112 +9481,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-115500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-23000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-84500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-96100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-152700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-40300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-31400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-37600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-88700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-204500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>201800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>38700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-36600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-56900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-260200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-171500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-143000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-184200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-332000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-102500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>50600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-119200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-138000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-103500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-27700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-96100</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ100" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9368,8 +9617,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9446,108 +9695,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-129000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>125700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-39300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>42300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-20500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>19400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-122700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>35900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>102700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1200</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -656,482 +656,495 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E7" s="2">
         <v>45689</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45598</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45507</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45416</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45325</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45227</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45136</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45045</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44954</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44863</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44772</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44590</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44499</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44317</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44226</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44044</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43953</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43862</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43771</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43680</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43589</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43498</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43407</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43316</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43225</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43134</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43036</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42945</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42763</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5153500</v>
+      </c>
+      <c r="E8" s="3">
         <v>5278500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5099400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5205400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4918500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5357300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4924700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4963500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4723100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4929600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4785300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5103800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4496400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4357800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4264100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4177200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3868200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3946600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3731700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3954100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3797600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3472300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3229400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3345800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3143100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3416900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3221700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3307100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3061700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3556000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3084200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3167500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2946800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3229800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2986200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4184000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4329500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4123900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4248800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4035100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4394000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4022200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4066700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3843200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4026400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3908200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4243800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3705800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3560600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3472900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3413600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3141500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3204000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2988400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3197800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3060900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2850100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2611800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2733100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2569000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2787900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2629600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2718600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2510300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2934700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2523300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2614200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2441300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2681700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2456200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>969500</v>
+      </c>
+      <c r="E10" s="3">
         <v>949000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>975500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>956600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>883400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>963300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>902500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>896800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>880000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>903200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>877100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>860000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>790600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>797200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>791200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>763600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>726700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>742600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>743300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>756300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>736700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>622200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>617600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>612700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>574100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>629000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>592100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>588500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>551400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>621300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>560900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>553300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>505500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>548100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1169,8 +1182,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1276,8 +1290,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1383,50 +1400,53 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>2600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7900</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1434,37 +1454,37 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>700</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>2800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
         <v>15100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1490,38 +1510,41 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E15" s="3">
         <v>67800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>65700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>65100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>63400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>61300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>57400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>54800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>54200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1597,8 +1620,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1633,222 +1659,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4948300</v>
+      </c>
+      <c r="E17" s="3">
         <v>5099000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4867900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4999800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4754500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5137800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4720100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4760100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4536400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4739400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4593600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4900900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4346100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4200700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4093900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4013400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3742600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3801900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3544100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3791800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3653900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3392300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3130500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3247100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3072500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3307000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3131300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3268400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2997100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3463300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3003700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3092700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2974600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3166900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2933100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>205200</v>
+      </c>
+      <c r="E18" s="3">
         <v>179500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>231500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>205600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>164100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>219500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>204600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>203500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>186800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>190200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>191700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>202900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>150300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>157100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>170200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>163800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>125600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>144700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>187600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>162300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>143700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>80000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>98900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>98700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>70600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>109900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>90400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>38700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>64600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>92700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>80500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>74800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-27800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>62900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1886,8 +1919,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1915,8 +1949,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1928,25 +1962,25 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5600</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-500</v>
       </c>
       <c r="W20" s="3">
         <v>-500</v>
@@ -1955,13 +1989,13 @@
         <v>-500</v>
       </c>
       <c r="Y20" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="Z20" s="3">
         <v>-600</v>
       </c>
       <c r="AA20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
@@ -1993,436 +2027,451 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>274800</v>
+      </c>
+      <c r="E21" s="3">
         <v>247400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>297200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>270700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>227500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>280800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>262000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>258300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>241000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>241900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>243800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>252900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>197400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>202500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>216500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>205700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>164900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>185700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>224100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>203100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>184100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>119600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>137500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>137100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>109400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>149700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>130300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>79800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>106000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>133400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>121700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>116000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>13300</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E22" s="3">
         <v>10300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>10900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7800</v>
-      </c>
-      <c r="P22" s="3">
-        <v>12400</v>
       </c>
       <c r="Q22" s="3">
         <v>12400</v>
       </c>
       <c r="R22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="S22" s="3">
         <v>12900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>13600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>13800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>17500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>25000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>26200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>27800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>26700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>33000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>59600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>45200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>46500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>42300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>43800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>64100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>35400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>35500</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>192500</v>
+      </c>
+      <c r="E23" s="3">
         <v>166300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>216800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>190900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>146800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>198400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>181400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>184000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>172100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>176500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>179500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>192000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>142500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>145300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>158300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>147400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>107000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>128800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>164500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>142900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>121900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>55900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>73200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>72000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>42900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>83100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>57300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-20900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>19400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>46200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>38200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>31000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-91900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>27500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E24" s="3">
         <v>43700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>61000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>45900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>35800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>52600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>50900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>52700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>56100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>47100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>48100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>51000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>30000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>37700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>31700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>36400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>25400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>32900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>41600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>36200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>26200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>13700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>18000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>17700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>19400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>10200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>15300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>11100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-33100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>10800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2528,222 +2577,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>149800</v>
+      </c>
+      <c r="E26" s="3">
         <v>122700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>155700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>145000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>111000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>145900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>130500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>131300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>116000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>129400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>131400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>141000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>112500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>107600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>126600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>111000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>81600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>95900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>122900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>106700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>95700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>42200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>55200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>54300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>36100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>63700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>52200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>14300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>36000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>22900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>19800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-58800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>16700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>149800</v>
+      </c>
+      <c r="E27" s="3">
         <v>122700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>155700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>145000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>111000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>145900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>130500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>131300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>116100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>129400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>131400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>141000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>112500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>107600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>126600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>111000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>81600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>95900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>122900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>106700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>95700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>42200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>55200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>54300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>36100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>63700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>52200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>14300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>36000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>22900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>19800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-58800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>16700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2849,8 +2907,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2876,17 +2937,17 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-1500</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
@@ -2894,11 +2955,11 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-100</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -2906,43 +2967,43 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V29" s="3">
         <v>-100</v>
       </c>
       <c r="W29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-300</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>600</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>2300</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-100</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-200</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>30700</v>
-      </c>
-      <c r="AG29" s="3">
-        <v>-100</v>
       </c>
       <c r="AH29" s="3">
         <v>-100</v>
@@ -2956,8 +3017,11 @@
       <c r="AK29" s="3">
         <v>-100</v>
       </c>
+      <c r="AL29" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3063,8 +3127,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3170,8 +3237,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3199,8 +3269,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3212,25 +3282,25 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5600</v>
-      </c>
-      <c r="V32" s="3">
-        <v>500</v>
       </c>
       <c r="W32" s="3">
         <v>500</v>
@@ -3239,13 +3309,13 @@
         <v>500</v>
       </c>
       <c r="Y32" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Z32" s="3">
         <v>600</v>
       </c>
       <c r="AA32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
@@ -3277,115 +3347,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>149800</v>
+      </c>
+      <c r="E33" s="3">
         <v>122700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>155700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>145000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>111000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>145900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>130500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>131300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>116100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>129800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>129900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>141000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>112500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>107600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>126500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>111000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>81600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>95900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>122800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>106600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>95700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>41800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>55100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>54500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>35800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>64300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>54400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>14100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>66700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>22800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>19700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-58900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>16600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3491,227 +3567,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>149800</v>
+      </c>
+      <c r="E35" s="3">
         <v>122700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>155700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>145000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>111000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>145900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>130500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>131300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>116100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>129800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>129900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>141000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>112500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>107600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>126500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>111000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>81600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>95900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>122800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>106600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>95700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>41800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>55100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>54500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>35800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>64300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>54400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>14100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>66700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>22800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>19700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-58900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>16600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E38" s="2">
         <v>45689</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45598</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45507</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45416</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45325</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45227</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45136</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45045</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44954</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44863</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44772</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44590</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44499</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44317</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44226</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44044</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43953</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43862</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43771</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43680</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43589</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43498</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43407</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43316</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43225</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43134</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43036</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42945</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42763</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3749,8 +3834,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3788,98 +3874,99 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E41" s="3">
         <v>28300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>38100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>35100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>163700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>38000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>45400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>84700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>42400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>63000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>43500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>46100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>168800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>132900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>30200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>30000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>29100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>29900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>27100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>31500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>31300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>30500</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3895,8 +3982,11 @@
       <c r="AK41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4002,98 +4092,101 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>240400</v>
+      </c>
+      <c r="E43" s="3">
         <v>277300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>266700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>248500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>225200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>234800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>224500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>200300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>217900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>239700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>252000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>204500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>210400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>174000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>200300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>169100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>198000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>172700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>188400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>170600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>193900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>206400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>186000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>162300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>180400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>194300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>179100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>165300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>168700</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4109,98 +4202,101 @@
       <c r="AK43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1567000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1509000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1720000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1546200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1533300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1454800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1661900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1540500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1532000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1378600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1504400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1376500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1462100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1242900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1255700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1033600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1120300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1205700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1264300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1005300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1024900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1081500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1271200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1026500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1085600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1052300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1245100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1005000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1055200</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4216,8 +4312,11 @@
       <c r="AK44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4245,69 +4344,69 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>51000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>72300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>57800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>58800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>54700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>58600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>46400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>54300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>48600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>97100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>64100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>46600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>42000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>55300</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>47400</v>
       </c>
       <c r="AA45" s="3">
         <v>47400</v>
       </c>
       <c r="AB45" s="3">
+        <v>47400</v>
+      </c>
+      <c r="AC45" s="3">
         <v>63500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>104300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>107300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>83000</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4323,98 +4422,101 @@
       <c r="AK45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1928800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1879000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2097100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1915100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1878700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1794000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2000500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1843300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1842300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1703200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1863300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1802500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1769300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1517100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1599300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1291600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1435500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1470600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1596000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1408800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1398400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1360000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1542400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1265300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1343200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1337200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1560000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1309000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1337500</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4430,8 +4532,11 @@
       <c r="AK46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4459,8 +4564,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4537,98 +4642,101 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4054200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3997900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3947000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3848100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3780200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3719300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3670600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3593700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3489400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3480000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3459700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3424700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3167400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3074300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3032200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2980200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2934900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2856600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2804000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2799400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2841200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2820300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2843300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2791600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2784500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>748800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>745900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>747700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>749700</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4644,98 +4752,101 @@
       <c r="AK48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1108500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1109900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1111600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1113200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1114800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1116400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1118400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1120400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1122400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1124300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1126600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1128900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1046500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1048800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1051400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1054000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1056600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1059300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1062200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1065200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1068200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1071100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1074500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1077900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1081200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1125000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1130800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1136700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1142800</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4751,8 +4862,11 @@
       <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4858,8 +4972,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4965,98 +5082,101 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E52" s="3">
         <v>71600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>55600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>50000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>48400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>43800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>40300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>33700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>28700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>27400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>21800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>22100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>25100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>20100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>20700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>20400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>18400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>17900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>17400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>17800</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>28300</v>
       </c>
       <c r="AC52" s="3">
         <v>28300</v>
       </c>
       <c r="AD52" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AE52" s="3">
         <v>27400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>31400</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5072,8 +5192,11 @@
       <c r="AK52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5179,98 +5302,101 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7157700</v>
+      </c>
+      <c r="E54" s="3">
         <v>7065300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7216200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6929900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6824700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6677600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6837200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6603900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6494500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6350000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6478900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6387200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6010000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5668900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5710200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5347600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5449200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5411500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5482300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5294000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5328100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5269800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5478100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5152100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5226700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3239300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3465000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3220900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3261300</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5286,8 +5412,11 @@
       <c r="AK54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5325,8 +5454,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5364,98 +5494,99 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1255900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1253500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1420400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1285700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1264900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1183300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1319000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1226500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1281700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1195700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1363700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1243300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1267100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1112800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1235800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1029700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1023100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>988100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1176100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1004700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>990400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>786400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>973300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>798500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>820500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>816900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>976500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>783100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>799500</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5471,50 +5602,53 @@
       <c r="AK57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>319600</v>
+      </c>
+      <c r="E58" s="3">
         <v>375800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>408300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>379800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>426900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>479700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>614500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>590400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>578900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>405000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>295000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>350000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>80000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5522,47 +5656,47 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>210000</v>
-      </c>
-      <c r="T58" s="3">
-        <v>260000</v>
       </c>
       <c r="U58" s="3">
         <v>260000</v>
       </c>
       <c r="V58" s="3">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>15400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>343400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>449400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>195400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>246400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>254400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>389400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>62300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>179300</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5578,98 +5712,101 @@
       <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>294200</v>
+      </c>
+      <c r="E59" s="3">
         <v>616300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>327500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>328300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>316600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>572200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>263800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>246600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>944600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>941200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>890900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>862000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>889700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>868300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>809500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>802800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>783100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>774300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>759500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>714400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>671600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>629100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>617200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>607000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>506400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>487900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>475600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>461200</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5685,98 +5822,101 @@
       <c r="AK59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2510400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2534100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2742000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2523800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2525800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2468000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2739100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2591100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2619300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2545300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2600000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2484100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2209100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2002500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2104100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1839200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2035900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2031200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2210400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1764200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1720200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1801400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2051800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1611100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1673900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1577700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1853800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1321000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1440000</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5792,98 +5932,101 @@
       <c r="AK60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2376100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2476400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2423400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2456700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2468100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2511800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2483100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2523200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2485800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>447900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>600100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>699400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>749000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>748600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>748100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>747700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>747300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>846200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>845700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1202200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1334800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1337300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1339700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1540600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1543500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1546500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1549400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1894100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2508000</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5899,98 +6042,101 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>241900</v>
+      </c>
+      <c r="E62" s="3">
         <v>132200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>219100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>218900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>222700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>143500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>189100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>194200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>190900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2309900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2335900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2350100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2330600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2269700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2290300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2272300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2252400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2214800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2208800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2208500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2240600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2185400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2191100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2165000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2157600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>317200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>318400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>323700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>324700</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6006,8 +6152,11 @@
       <c r="AK62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6113,8 +6262,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6220,8 +6372,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6327,98 +6482,101 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5186100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5217900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5454100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5275000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5297300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5218800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5483500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5372600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5362800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5303100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5536000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5533700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5288700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5020800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5142500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4859200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5035700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5092200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5264900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5174900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5295600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5324100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5582600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5316700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5375000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3441400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3721600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3538700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4272700</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6434,8 +6592,11 @@
       <c r="AK66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6473,8 +6634,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6580,8 +6742,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6687,8 +6852,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6794,8 +6962,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6901,98 +7072,101 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1852400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1702600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1580000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1424200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1279300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1168200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1022400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>891900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>760600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>644500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>514700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>384800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>243800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>131300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>23700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-102800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-213800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-295300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-391200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-514000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-620600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-716400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-758100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-813200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-867700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-915100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-979400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1033900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1028200</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7008,8 +7182,11 @@
       <c r="AK72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7115,8 +7292,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7222,8 +7402,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7329,98 +7512,101 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1971600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1847500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1762200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1654900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1527400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1458900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1353700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1231300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1131700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1046800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>942900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>853600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>721300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>648100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>567700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>488400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>413500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>319300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>217400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>119100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>32500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-54300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-104500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-164600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-148300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-202100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-256600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-317900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-1011400</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7436,8 +7622,11 @@
       <c r="AK76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7543,227 +7732,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E80" s="2">
         <v>45689</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45598</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45507</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45416</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45325</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45227</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45136</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45045</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44954</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44863</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44772</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44590</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44499</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44317</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44226</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44044</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43953</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43862</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43771</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43680</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43589</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43498</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43407</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43316</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43225</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43134</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43036</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42945</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42763</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>149800</v>
+      </c>
+      <c r="E81" s="3">
         <v>122700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>155700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>145000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>111000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>145900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>130500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>131300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>116100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>129800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>129900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>141000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>112500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>107600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>126500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>111000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>81600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>95900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>122800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>106600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>95700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>41800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>55100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>54500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>35800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>64300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>54400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>14100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>66700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>22800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>19700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-58900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>16600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7801,115 +7999,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E83" s="3">
         <v>53400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>57400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>54800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>54200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>42500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>52200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>50000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>47100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>51700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>52200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>50000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>47100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>44900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>45800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>45400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>44400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>43100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>42200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>41300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>40800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>40100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>39200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>39000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>38700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>39800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>39900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>41100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>41400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>40700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>41100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>41200</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK83" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8015,8 +8217,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8122,8 +8327,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8229,8 +8437,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8336,8 +8547,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8443,115 +8657,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>208100</v>
+      </c>
+      <c r="E89" s="3">
         <v>271900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>206800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>221400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>200800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>274400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>175000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>150400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>119100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>175300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>169800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>398700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>44300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>98500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>173900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>310300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>249000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>66600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>68300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>263800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>469900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>133600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>170200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>44900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>176200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>47700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>137900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>65400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>109700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>46400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>119100</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK89" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8589,115 +8809,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-140500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-160400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-187900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-133900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-105700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-119100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-133700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-122200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-92100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-103500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-102800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-101000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-90500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-101100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-74700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-73100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-74700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-65500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-69800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-47800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-35200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-52500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-56100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-51800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-36500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-42600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-27700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-51300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-21800</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK91" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL91" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8803,8 +9027,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8910,115 +9137,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-142300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-162000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-187900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-133900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-105700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-119100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-127400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-116200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-92100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-87300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-94400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-474800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-90500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-101100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-74700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-70700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-58100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-65500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-48000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-43700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-30900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-56100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-51800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-36500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-33500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-42100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-51300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK94" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9056,16 +9289,17 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>8</v>
@@ -9073,11 +9307,11 @@
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
@@ -9085,8 +9319,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9149,22 +9383,25 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-100</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9270,8 +9507,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9377,8 +9617,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9484,115 +9727,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-115500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-23000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-84500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-96100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-152700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-40300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-31400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-37600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-88700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-204500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>201800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>38700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-36600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-56900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-260200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-171500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-143000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-184200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-332000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-102500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>50600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-119200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-138000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-103500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-27700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-96100</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK100" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9620,8 +9869,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9698,111 +9947,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-129000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>125700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-39300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>42300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-20500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>19400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-122700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>35900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>102700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1200</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -656,520 +656,533 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45962</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45871</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45780</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45689</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45598</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45507</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45416</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45325</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45227</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45136</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45045</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44954</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44863</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44772</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44590</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44499</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44317</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44226</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44044</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43953</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43862</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43771</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43680</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43589</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43498</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43407</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43316</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43225</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43134</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43036</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42945</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42854</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42763</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5575400</v>
+      </c>
+      <c r="E8" s="3">
         <v>5348200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5380200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5153500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5278500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5099400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5205400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4918500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5357300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4924700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4963500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4723100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4929600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4785300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5103800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4496400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4357800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4264100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4177200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3868200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3946600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3731700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3954100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3797600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3472300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3229400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3345800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3143100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3416900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3221700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3307100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3061700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3556000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3084200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3167500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2946800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3229800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2986200</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4565800</v>
+      </c>
+      <c r="E9" s="3">
         <v>4333800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4374100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4184000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4329500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4123900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4248800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4035100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4394000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4022200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4066700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3843200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4026400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3908200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4243800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3705800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3560600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3472900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3413600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3141500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3204000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2988400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3197800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3060900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2850100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2611800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2733100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2569000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2787900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2629600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2718600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2510300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2934700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2523300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2614200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2441300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2681700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2456200</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1009600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1014300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1006200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>969500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>949000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>975500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>956600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>883400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>963300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>902500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>896800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>880000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>903200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>877100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>860000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>790600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>797200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>791200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>763600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>726700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>742600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>743300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>756300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>736700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>622200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>617600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>612700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>574100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>629000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>592100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>588500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>551400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>621300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>560900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>553300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>505500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>548100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1210,8 +1223,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1326,8 +1340,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1442,59 +1459,62 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>2600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7900</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1502,37 +1522,37 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>700</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>2800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1300</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>15100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1558,47 +1578,50 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E15" s="3">
         <v>72300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>71900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>69700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>67800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>65700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>65100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>63400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>61300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>57400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>54800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>54200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1674,8 +1697,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1713,240 +1739,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5397300</v>
+      </c>
+      <c r="E17" s="3">
         <v>5128300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5162700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4948300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5099000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4867900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4999800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4754500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5137800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4720100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4760100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4536400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4739400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4593600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4900900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4346100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4200700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4093900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4013400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3742600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3801900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3544100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3791800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3653900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3392300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3130500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3247100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3072500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3307000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3131300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3268400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2997100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3463300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3003700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3092700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2974600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3166900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2933100</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>178100</v>
+      </c>
+      <c r="E18" s="3">
         <v>219800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>217600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>205200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>179500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>231500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>205600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>164100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>219500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>204600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>203500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>186800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>190200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>191700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>202900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>150300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>157100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>170200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>163800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>125600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>144700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>187600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>162300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>143700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>80000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>98900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>98700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>70600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>109900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>90400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>38700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>64600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>92700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>80500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>74800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-27800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>62900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1987,8 +2020,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2025,8 +2059,8 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -2038,25 +2072,25 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5600</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-500</v>
       </c>
       <c r="Z20" s="3">
         <v>-500</v>
@@ -2065,13 +2099,13 @@
         <v>-500</v>
       </c>
       <c r="AB20" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="AC20" s="3">
         <v>-600</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
@@ -2103,472 +2137,487 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>252800</v>
+      </c>
+      <c r="E21" s="3">
         <v>292200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>289500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>274800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>247400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>297200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>270700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>227500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>280800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>262000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>258300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>241000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>241900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>243800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>252900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>197400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>202500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>216500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>205700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>164900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>185700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>224100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>203100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>184100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>119600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>137500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>137100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>109400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>149700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>130300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>79800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>106000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>133400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>121700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>116000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>13300</v>
       </c>
-      <c r="AM21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E22" s="3">
         <v>10300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>18000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>13700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7800</v>
-      </c>
-      <c r="S22" s="3">
-        <v>12400</v>
       </c>
       <c r="T22" s="3">
         <v>12400</v>
       </c>
       <c r="U22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="V22" s="3">
         <v>12900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>17500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>18900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>21300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>25000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>26200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>27800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>26700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>33000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>59600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>45200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>42300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>43800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>64100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>35400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>35500</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>167500</v>
+      </c>
+      <c r="E23" s="3">
         <v>208000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>206100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>192500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>166300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>216800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>190900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>146800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>198400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>181400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>184000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>172100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>176500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>179500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>192000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>142500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>145300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>158300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>147400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>107000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>128800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>164500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>142900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>121900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>55900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>73200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>72000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>42900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>83100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>57300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-20900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>19400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>46200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>38200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>31000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-91900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>27500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E24" s="3">
         <v>56000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>55400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>42800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>43700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>45900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>35800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>52600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>50900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>52700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>56100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>47100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>48100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>51000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>30000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>37700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>31700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>36400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>25400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>32900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>41600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>36200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>26200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>13700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>18000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>17700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>19400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>15300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>11100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-33100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>10800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2683,240 +2732,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E26" s="3">
         <v>152100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>150700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>149800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>122700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>155700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>145000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>111000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>145900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>130500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>131300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>116000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>129400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>131400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>141000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>112500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>107600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>126600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>111000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>81600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>95900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>122900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>106700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>95700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>42200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>55200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>54300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>36100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>63700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>52200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>14300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>36000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>22900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>19800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-58800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>16700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E27" s="3">
         <v>152100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>150700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>149800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>122700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>155700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>145000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>111000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>145900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>130500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>131300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>116100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>129400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>131400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>141000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>112500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>107600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>126600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>111000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>81600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>95900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>122900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>106700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>95700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>42200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>55200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>54300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>36100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>63700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>52200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>14300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>36000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>22900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>19800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-58800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>16700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3031,8 +3089,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3067,17 +3128,17 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
@@ -3085,11 +3146,11 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-100</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
@@ -3097,43 +3158,43 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="3">
         <v>-100</v>
       </c>
       <c r="Z29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-300</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>2300</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-100</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-200</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>30700</v>
-      </c>
-      <c r="AJ29" s="3">
-        <v>-100</v>
       </c>
       <c r="AK29" s="3">
         <v>-100</v>
@@ -3147,8 +3208,11 @@
       <c r="AN29" s="3">
         <v>-100</v>
       </c>
+      <c r="AO29" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3263,8 +3327,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3379,8 +3446,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3417,8 +3487,8 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3430,25 +3500,25 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5600</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>500</v>
       </c>
       <c r="Z32" s="3">
         <v>500</v>
@@ -3457,13 +3527,13 @@
         <v>500</v>
       </c>
       <c r="AB32" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AC32" s="3">
         <v>600</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
@@ -3495,124 +3565,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E33" s="3">
         <v>152100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>150700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>149800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>122700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>155700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>145000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>111000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>145900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>130500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>131300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>116100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>129800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>129900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>141000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>112500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>107600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>126500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>111000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>81600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>95900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>122800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>106600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>95700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>41800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>55100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>54500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>35800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>64300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>54400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>14100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>66700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>22800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>19700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-58900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>16600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3727,245 +3803,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E35" s="3">
         <v>152100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>150700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>149800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>122700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>155700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>145000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>111000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>145900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>130500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>131300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>116100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>129800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>129900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>141000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>112500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>107600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>126500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>111000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>81600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>95900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>122800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>106600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>95700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>41800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>55100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>54500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>35800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>64300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>54400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>14100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>66700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>22800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>19700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-58900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>16600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45962</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45871</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45780</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45689</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45598</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45507</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45416</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45325</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45227</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45136</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45045</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44954</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44863</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44772</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44590</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44499</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44317</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44226</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44044</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43953</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43862</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43771</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43680</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43589</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43498</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43407</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43316</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43225</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43134</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43036</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42945</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42854</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42763</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4006,8 +4091,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4048,107 +4134,108 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E41" s="3">
         <v>45100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>47300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>38100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>23400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>163700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>38000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>45400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>84700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>42400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>63000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>43500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>46100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>168800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>132900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>30200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>30000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>29100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>29900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>27100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>31500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>31300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>30500</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
@@ -4164,8 +4251,11 @@
       <c r="AN41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4280,107 +4370,110 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>252800</v>
+      </c>
+      <c r="E43" s="3">
         <v>299300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>270900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>240400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>277300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>266700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>248500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>225200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>234800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>224500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>217900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>239700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>252000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>204500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>210400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>174000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>200300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>169100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>198000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>172700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>188400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>170600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>193900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>206400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>186000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>162300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>180400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>194300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>179100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>165300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>168700</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4396,107 +4489,110 @@
       <c r="AN43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1555500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1693800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1520700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1567000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1509000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1720000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1546200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1533300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1454800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1661900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1540500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1532000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1378600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1504400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1376500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1462100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1242900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1255700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1033600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1120300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1205700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1264300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1005300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1024900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1081500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1271200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1026500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1085600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1052300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1245100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1005000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1055200</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4512,8 +4608,11 @@
       <c r="AN44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4550,69 +4649,69 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>51000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>72300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>57800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>58800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>54700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>58600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>46400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>54300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>48600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>97100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>64100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>46600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>42000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>55300</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>47400</v>
       </c>
       <c r="AD45" s="3">
         <v>47400</v>
       </c>
       <c r="AE45" s="3">
+        <v>47400</v>
+      </c>
+      <c r="AF45" s="3">
         <v>63500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>104300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>107300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>83000</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4628,107 +4727,110 @@
       <c r="AN45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1990100</v>
+      </c>
+      <c r="E46" s="3">
         <v>2128600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1929000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1928800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1879000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2097100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1915100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1878700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1794000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2000500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1843300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1842300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1703200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1863300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1802500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1769300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1517100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1599300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1291600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1435500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1470600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1596000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1408800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1398400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1360000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1542400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1265300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1343200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1337200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1560000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1309000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1337500</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4744,8 +4846,11 @@
       <c r="AN46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4782,8 +4887,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4860,107 +4965,110 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4340600</v>
+      </c>
+      <c r="E48" s="3">
         <v>4243200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4122800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4054200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3997900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3947000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3848100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3780200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3719300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3670600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3593700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3489400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3480000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3459700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3424700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3167400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3074300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3032200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2980200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2934900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2856600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2804000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2799400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2841200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2820300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2843300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2791600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2784500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>748800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>745900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>747700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>749700</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4976,107 +5084,110 @@
       <c r="AN48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1104300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1105700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1107100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1108500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1109900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1111600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1113200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1114800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1116400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1118400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1120400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1122400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1124300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1126600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1128900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1046500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1048800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1051400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1054000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1056600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1059300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1062200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1065200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1068200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1071100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1074500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1077900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1081200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1125000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1130800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1136700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1142800</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5092,8 +5203,11 @@
       <c r="AN49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5208,8 +5322,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5324,107 +5441,110 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E52" s="3">
         <v>62400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>67100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>58600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>71600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>55600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>50000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>48400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>43800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>40300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>33700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>42400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>31100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>26800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>28700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>27400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>21800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>22100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>25100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>20100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>20700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>20400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>18400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>17900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>17400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>17800</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>28300</v>
       </c>
       <c r="AF52" s="3">
         <v>28300</v>
       </c>
       <c r="AG52" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AH52" s="3">
         <v>27400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>31400</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5440,8 +5560,11 @@
       <c r="AN52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5556,107 +5679,110 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7510500</v>
+      </c>
+      <c r="E54" s="3">
         <v>7545800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7231800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7157700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7065300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7216200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6929900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6824700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6677600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6837200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6603900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6494500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6350000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6478900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6387200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6010000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5668900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5710200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5347600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5449200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5411500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5482300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5294000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5328100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5269800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5478100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5152100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5226700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3239300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3465000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3220900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3261300</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5672,8 +5798,11 @@
       <c r="AN54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5714,8 +5843,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5756,107 +5886,108 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1307400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1376100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1264200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1255900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1253500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1420400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1285700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1264900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1183300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1319000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1226500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1281700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1195700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1363700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1243300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1267100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1112800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1235800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1029700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1023100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>988100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1176100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1004700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>990400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>786400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>973300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>798500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>820500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>816900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>976500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>783100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>799500</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5872,59 +6003,62 @@
       <c r="AN57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>341500</v>
+      </c>
+      <c r="E58" s="3">
         <v>377900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>278500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>319600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>375800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>408300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>379800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>426900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>479700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>614500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>590400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>578900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>405000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>295000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>350000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>80000</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
@@ -5932,47 +6066,47 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>210000</v>
-      </c>
-      <c r="W58" s="3">
-        <v>260000</v>
       </c>
       <c r="X58" s="3">
         <v>260000</v>
       </c>
       <c r="Y58" s="3">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>15400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>343400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>449400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>195400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>246400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>254400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>389400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>62300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>179300</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5988,107 +6122,110 @@
       <c r="AN58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>634500</v>
+      </c>
+      <c r="E59" s="3">
         <v>299400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>300700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>294200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>616300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>327500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>328300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>316600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>572200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>263800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>246600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3">
         <v>944600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>941200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>890900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>862000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>889700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>868300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>809500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>802800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>783100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>774300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>759500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>714400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>671600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>629100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>617200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>607000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>506400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>487900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>475600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>461200</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
@@ -6104,107 +6241,110 @@
       <c r="AN59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2670200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2699700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2434200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2510400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2534100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2742000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2523800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2525800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2468000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2739100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2591100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2619300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2545300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2600000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2484100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2209100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2002500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2104100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1839200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2035900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2031200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2210400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1764200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1720200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1801400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2051800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1611100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1673900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1577700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1853800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1321000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1440000</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>8</v>
       </c>
@@ -6220,107 +6360,110 @@
       <c r="AN60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2396800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2319200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2358300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2376100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2476400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2423400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2456700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2468100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2511800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2483100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2523200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2485800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>447900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>600100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>699400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>749000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>748600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>748100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>747700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>747300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>846200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>845700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1202200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1334800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1337300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1339700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1540600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1543500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1546500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1549400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1894100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2508000</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
@@ -6336,107 +6479,110 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>162800</v>
+      </c>
+      <c r="E62" s="3">
         <v>283900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>269900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>241900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>132200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>219100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>218900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>222700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>143500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>189100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>194200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>190900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2309900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2335900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2350100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2330600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2269700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2290300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2272300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2252400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2214800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2208800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2208500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2240600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2185400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2191100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2165000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2157600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>317200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>318400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>323700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>324700</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6452,8 +6598,11 @@
       <c r="AN62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6568,8 +6717,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6684,8 +6836,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6800,107 +6955,110 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5312800</v>
+      </c>
+      <c r="E66" s="3">
         <v>5373900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5132700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5186100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5217900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5454100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5275000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5297300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5218800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5483500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5372600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5362800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5303100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5536000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5533700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5288700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5020800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5142500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4859200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5035700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5092200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5264900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5174900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5295600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5324100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5582600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5316700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5375000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3441400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3721600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3538700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4272700</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6916,8 +7074,11 @@
       <c r="AN66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6958,8 +7119,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7074,8 +7236,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7190,8 +7355,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7306,8 +7474,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7422,107 +7593,110 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1201200</v>
+      </c>
+      <c r="E72" s="3">
         <v>2155200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2003100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1852400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1702600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1580000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1424200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1279300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1168200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1022400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>891900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>760600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>644500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>514700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>384800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>243800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>131300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>23700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-102800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-213800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-295300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-391200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-514000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-620600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-716400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-758100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-813200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-867700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-915100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-979400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-1033900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-1028200</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7538,8 +7712,11 @@
       <c r="AN72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7654,8 +7831,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7770,8 +7950,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7886,107 +8069,110 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2197700</v>
+      </c>
+      <c r="E76" s="3">
         <v>2171900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2099100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1971600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1847500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1762200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1654900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1527400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1458900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1353700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1231300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1131700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1046800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>942900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>853600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>721300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>648100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>567700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>488400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>413500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>319300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>217400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>119100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>32500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-54300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-104500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-164600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-148300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-202100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-256600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-317900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-1011400</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>8</v>
       </c>
@@ -8002,8 +8188,11 @@
       <c r="AN76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8118,245 +8307,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45962</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45871</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45780</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45689</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45598</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45507</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45416</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45325</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45227</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45136</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45045</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44954</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44863</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44772</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44590</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44499</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44317</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44226</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44044</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43953</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43862</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43771</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43680</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43589</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43498</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43407</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43316</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43225</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43134</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43036</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42945</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42854</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42763</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>125900</v>
+      </c>
+      <c r="E81" s="3">
         <v>152100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>150700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>149800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>122700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>155700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>145000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>111000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>145900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>130500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>131300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>116100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>129800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>129900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>141000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>112500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>107600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>126500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>111000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>81600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>95900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>122800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>106600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>95700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>41800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>55100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>54500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>35800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>64300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>54400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>14100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>66700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>22800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>19700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-58900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>16600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8397,124 +8595,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E83" s="3">
         <v>65700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>65100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>63400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>53400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>57400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>54800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>54200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>42500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>52200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>50000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>47100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>51700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>52200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>50000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>47100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>44900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>45800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>45400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>44400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>43100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>42200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>41300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>40800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>40100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>39200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>39000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>38700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>39800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>39900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>41100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>41400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>40700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>41100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>41200</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN83" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO83" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8629,8 +8831,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8745,8 +8950,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8861,8 +9069,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8977,8 +9188,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9093,124 +9307,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>391000</v>
+      </c>
+      <c r="E89" s="3">
         <v>181100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>249900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>208100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>271900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>206800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>221400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>200800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>274400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>175000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>150400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>119100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>175300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>169800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>398700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>44300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>98500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>173900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>310300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>249000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>66600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>68300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>263800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>469900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>133600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>170200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>44900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>176200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>47700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>137900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>65400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>109700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>46400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>119100</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN89" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO89" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9251,124 +9471,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-201100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-194900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-165600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-140500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-160400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-187900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-133900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-105700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-119100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-133700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-122200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-92100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-103500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-102800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-101000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-90500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-101100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-74700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-73100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-74700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-65500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-69800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-47800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-35200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-52500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-56100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-51800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-36500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-27700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-51300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-21800</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN91" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO91" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9483,8 +9707,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9599,124 +9826,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-201200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-195000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-163900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-142300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-162000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-187900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-133900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-105700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-119100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-127400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-116200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-92100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-87300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-94400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-474800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-90500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-101100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-74700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-70700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-58100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-65500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-48000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-43700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-35200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-30900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-56100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-51800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-36500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-33500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-42100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-51300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN94" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO94" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9757,8 +9990,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9771,8 +10005,8 @@
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
@@ -9783,11 +10017,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>8</v>
@@ -9795,8 +10029,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9859,22 +10093,25 @@
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-100</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9989,8 +10226,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10105,8 +10345,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10221,124 +10464,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-188700</v>
+      </c>
+      <c r="E100" s="3">
         <v>11700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-78200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-54600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-115500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-23000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-84500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-96100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-152700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-40300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-31400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-37600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-88700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-204500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>201800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>38700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-36600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-56900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-260200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-171500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-143000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-184200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-332000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-102500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>50600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-119200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-138000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-103500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-27700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-96100</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN100" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO100" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10375,8 +10624,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10453,120 +10702,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-129000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>125700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-39300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>42300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-20500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>19400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-122700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>35900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>102700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1200</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BJ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
   <si>
     <t>BJ</t>
   </si>
@@ -656,533 +656,546 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46144</v>
+      </c>
+      <c r="E7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45962</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45871</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45780</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45689</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45598</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45507</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45416</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45325</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45227</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45136</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45045</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44954</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44863</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44772</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44590</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44499</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44317</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44226</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44044</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43953</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43862</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43771</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43680</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43589</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43498</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43407</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43316</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43134</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43036</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42945</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42854</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42763</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5661500</v>
+      </c>
+      <c r="E8" s="3">
         <v>5575400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5348200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5380200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5153500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5278500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5099400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5205400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4918500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5357300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4924700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4963500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4723100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4929600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4785300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5103800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4496400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4357800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4264100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4177200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3868200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3946600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3731700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3954100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3797600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3472300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3229400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3345800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3143100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3416900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3221700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3307100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3061700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3556000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3084200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3167500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2946800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3229800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2986200</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4633600</v>
+      </c>
+      <c r="E9" s="3">
         <v>4565800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4333800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4374100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4184000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4329500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4123900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4248800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4035100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4394000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4022200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4066700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3843200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4026400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3908200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4243800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3705800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3560600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3472900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3413600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3141500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3204000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2988400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3197800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3060900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2850100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2611800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2733100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2569000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2787900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2629600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2718600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2510300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2934700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2523300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2614200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2441300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2681700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2456200</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1027900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1009600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1014300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1006200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>969500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>949000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>975500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>956600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>883400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>963300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>902500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>896800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>880000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>903200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>877100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>860000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>790600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>797200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>791200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>763600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>726700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>742600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>743300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>756300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>736700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>622200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>617600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>612700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>574100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>629000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>592100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>588500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>551400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>621300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>560900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>553300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>505500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>548100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>530000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1224,8 +1237,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1343,8 +1357,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1462,62 +1479,65 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7900</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1525,37 +1545,37 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>700</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1300</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>15100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1581,50 +1601,53 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E15" s="3">
         <v>74700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>72300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>71900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>69700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>67800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>65700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>65100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>63400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>61300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>57400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>54800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>54200</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1700,8 +1723,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1740,246 +1766,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5453600</v>
+      </c>
+      <c r="E17" s="3">
         <v>5397300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5128300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5162700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4948300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5099000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4867900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4999800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4754500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5137800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4720100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4760100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4536400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4739400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4593600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4900900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4346100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4200700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4093900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4013400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3742600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3801900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3544100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3791800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3653900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3392300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3130500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3247100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3072500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3307000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3131300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3268400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2997100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3463300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3003700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3092700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2974600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3166900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2933100</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>207900</v>
+      </c>
+      <c r="E18" s="3">
         <v>178100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>219800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>217600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>205200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>179500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>231500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>205600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>164100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>219500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>204600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>203500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>186800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>190200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>191700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>202900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>150300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>157100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>170200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>163800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>125600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>144700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>187600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>162300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>143700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>80000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>98900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>98700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>70600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>109900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>90400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>38700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>64600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>92700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>80500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>74800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-27800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>62900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2021,8 +2054,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2062,8 +2096,8 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -2075,25 +2109,25 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5600</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-500</v>
       </c>
       <c r="AA20" s="3">
         <v>-500</v>
@@ -2102,13 +2136,13 @@
         <v>-500</v>
       </c>
       <c r="AC20" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="AD20" s="3">
         <v>-600</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
@@ -2140,484 +2174,499 @@
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>284400</v>
+      </c>
+      <c r="E21" s="3">
         <v>252800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>292200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>289500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>274800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>247400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>297200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>270700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>227500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>280800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>262000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>258300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>241000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>241900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>243800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>252900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>197400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>202500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>216500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>205700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>164900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>185700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>224100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>203100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>184100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>119600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>137500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>137100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>109400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>149700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>130300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>79800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>106000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>133400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>121700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>116000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>13300</v>
       </c>
-      <c r="AN21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AO21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E22" s="3">
         <v>9700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>13700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>10900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7800</v>
-      </c>
-      <c r="T22" s="3">
-        <v>12400</v>
       </c>
       <c r="U22" s="3">
         <v>12400</v>
       </c>
       <c r="V22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="W22" s="3">
         <v>12900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>17500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>18900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>21300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>23600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>26200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>27800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>26700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>33000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>59600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>45200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>46500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>42300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>43800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>64100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>35400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>35500</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>195500</v>
+      </c>
+      <c r="E23" s="3">
         <v>167500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>208000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>206100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>192500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>166300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>216800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>190900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>146800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>198400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>181400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>184000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>172100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>176500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>179500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>192000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>142500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>145300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>158300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>147400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>107000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>128800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>164500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>142900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>121900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>55900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>73200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>72000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>42900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>83100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>57300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-20900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>19400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>46200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>38200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>31000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-91900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>27500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E24" s="3">
         <v>41600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>56000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>55400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>42800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>43700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>61000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>45900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>35800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>52600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>50900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>52700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>56100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>47100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>48100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>51000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>30000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>37700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>31700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>36400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>25400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>32900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>41600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>36200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>26200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>13700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>18000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>17700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>19400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>5100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-15400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>10200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>15300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>11100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-33100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>10800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2735,246 +2784,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>142700</v>
+      </c>
+      <c r="E26" s="3">
         <v>125900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>152100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>150700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>149800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>122700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>155700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>145000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>111000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>145900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>130500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>131300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>116000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>129400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>131400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>141000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>112500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>107600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>126600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>111000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>81600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>95900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>122900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>106700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>95700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>42200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>55200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>54300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>36100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>63700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>52200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>36000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>22900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>19800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-58800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>16700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>142700</v>
+      </c>
+      <c r="E27" s="3">
         <v>125900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>152100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>150700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>149800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>122700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>155700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>145000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>111000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>145900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>130500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>131300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>116100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>129400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>131400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>141000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>112500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>107600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>126600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>111000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>81600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>95900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>122900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>106700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>95700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>42200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>55200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>54300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>36100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>63700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>52200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>36000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>22900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>19800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-58800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>16700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3092,8 +3150,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3131,17 +3192,17 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-1500</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -3149,11 +3210,11 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-100</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
@@ -3161,43 +3222,43 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="3">
         <v>-100</v>
       </c>
       <c r="AA29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-300</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>600</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>2300</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>30700</v>
-      </c>
-      <c r="AK29" s="3">
-        <v>-100</v>
       </c>
       <c r="AL29" s="3">
         <v>-100</v>
@@ -3211,8 +3272,11 @@
       <c r="AO29" s="3">
         <v>-100</v>
       </c>
+      <c r="AP29" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3330,8 +3394,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3449,8 +3516,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3490,8 +3560,8 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3503,25 +3573,25 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5600</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>500</v>
       </c>
       <c r="AA32" s="3">
         <v>500</v>
@@ -3530,13 +3600,13 @@
         <v>500</v>
       </c>
       <c r="AC32" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AD32" s="3">
         <v>600</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
@@ -3568,127 +3638,133 @@
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>142700</v>
+      </c>
+      <c r="E33" s="3">
         <v>125900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>152100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>150700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>149800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>122700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>155700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>145000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>111000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>145900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>130500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>131300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>116100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>129800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>129900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>141000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>112500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>107600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>126500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>111000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>81600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>95900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>122800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>106600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>95700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>41800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>55100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>54500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>35800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>64300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>54400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>66700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>22800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>19700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-58900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>16600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3806,251 +3882,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>142700</v>
+      </c>
+      <c r="E35" s="3">
         <v>125900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>152100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>150700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>149800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>122700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>155700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>145000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>111000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>145900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>130500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>131300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>116100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>129800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>129900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>141000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>112500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>107600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>126500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>111000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>81600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>95900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>122800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>106600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>95700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>41800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>55100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>54500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>35800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>64300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>54400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>66700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>22800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>19700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-58900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>16600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46144</v>
+      </c>
+      <c r="E38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45962</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45871</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45780</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45689</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45598</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45507</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45416</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45325</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45227</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45136</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45045</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44954</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44863</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44772</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44590</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44499</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44317</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44226</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44044</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43953</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43862</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43771</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43680</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43589</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43498</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43407</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43316</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43134</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43036</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42945</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42854</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42763</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4092,8 +4177,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4135,110 +4221,111 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E41" s="3">
         <v>46200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>45100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>47300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>39500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>28300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>38100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>33600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>33900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>34600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>163700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>38000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>45400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>84700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>42400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>63000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>46100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>168800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>132900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>30200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>30000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>29100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>29900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>27100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>31500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>31300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>30500</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>8</v>
       </c>
@@ -4254,8 +4341,11 @@
       <c r="AO41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4373,110 +4463,113 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>319900</v>
+      </c>
+      <c r="E43" s="3">
         <v>252800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>299300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>270900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>240400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>277300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>266700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>248500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>225200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>234800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>224500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>200300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>217900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>239700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>252000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>204500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>210400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>174000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>200300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>169100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>198000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>172700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>188400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>170600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>193900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>206400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>186000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>162300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>180400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>194300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>179100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>165300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>168700</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4492,110 +4585,113 @@
       <c r="AO43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1668300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1555500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1693800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1520700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1567000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1509000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1720000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1546200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1533300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1454800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1661900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1540500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1532000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1378600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1504400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1376500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1462100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1242900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1255700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1033600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1120300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1205700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1264300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1005300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1024900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1081500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1271200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1026500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1085600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1052300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1245100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1005000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1055200</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4611,8 +4707,11 @@
       <c r="AO44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4652,69 +4751,69 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>51000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>72300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>57800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>58800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>54700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>58600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>46400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>54300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>48600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>97100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>64100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>46600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>42000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>55300</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>47400</v>
       </c>
       <c r="AE45" s="3">
         <v>47400</v>
       </c>
       <c r="AF45" s="3">
+        <v>47400</v>
+      </c>
+      <c r="AG45" s="3">
         <v>63500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>104300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>107300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>83000</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4730,110 +4829,113 @@
       <c r="AO45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2214900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1990100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2128600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1929000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1928800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1879000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2097100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1915100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1878700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1794000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2000500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1843300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1842300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1703200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1863300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1802500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1769300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1517100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1599300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1291600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1435500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1470600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1596000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1408800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1398400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1360000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1542400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1265300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1343200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1337200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1560000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1309000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1337500</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4849,8 +4951,11 @@
       <c r="AO46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4890,8 +4995,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4968,110 +5073,113 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4538900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4340600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4243200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4122800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4054200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3997900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3947000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3848100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3780200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3719300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3670600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3593700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3489400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3480000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3459700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3424700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3167400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3074300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3032200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2980200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2934900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2856600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2804000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2799400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2841200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2820300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2843300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2791600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2784500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>748800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>745900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>747700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>749700</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>8</v>
       </c>
@@ -5087,110 +5195,113 @@
       <c r="AO48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1103100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1104300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1105700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1107100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1108500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1109900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1111600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1113200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1114800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1116400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1118400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1120400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1122400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1124300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1126600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1128900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1046500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1048800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1051400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1054000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1056600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1059300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1062200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1065200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1068200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1071100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1074500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1077900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1081200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1125000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1130800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1136700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1142800</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5206,8 +5317,11 @@
       <c r="AO49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5325,8 +5439,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5444,110 +5561,113 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E52" s="3">
         <v>71100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>62400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>67100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>58600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>71600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>55600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>50000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>48400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>43800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>40300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>38600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>33700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>31100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>26800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>28700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>27400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>21800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>22100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>25100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>20100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>20700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>18400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>17900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>17400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>17800</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>28300</v>
       </c>
       <c r="AG52" s="3">
         <v>28300</v>
       </c>
       <c r="AH52" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AI52" s="3">
         <v>27400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>31400</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5563,8 +5683,11 @@
       <c r="AO52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5682,110 +5805,113 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7929000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7510500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7545800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7231800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7157700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7065300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7216200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6929900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6824700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6677600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6837200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6603900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6494500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6350000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6478900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6387200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6010000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5668900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5710200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5347600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5449200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5411500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5482300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5294000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5328100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5269800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5478100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5152100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5226700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3239300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3465000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3220900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3261300</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5801,8 +5927,11 @@
       <c r="AO54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5844,8 +5973,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5887,110 +6017,111 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1438900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1307400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1376100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1264200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1255900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1253500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1420400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1285700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1264900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1183300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1319000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1226500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1281700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1195700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1363700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1243300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1267100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1112800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1235800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1029700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1023100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>988100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1176100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1004700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>990400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>786400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>973300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>798500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>820500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>816900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>976500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>783100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>799500</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK57" s="3" t="s">
         <v>8</v>
       </c>
@@ -6006,62 +6137,65 @@
       <c r="AO57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>557000</v>
+      </c>
+      <c r="E58" s="3">
         <v>341500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>377900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>278500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>319600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>375800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>408300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>379800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>426900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>479700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>614500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>590400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>578900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>405000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>295000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>350000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>80000</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
@@ -6069,47 +6203,47 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>210000</v>
-      </c>
-      <c r="X58" s="3">
-        <v>260000</v>
       </c>
       <c r="Y58" s="3">
         <v>260000</v>
       </c>
       <c r="Z58" s="3">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>15400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>343400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>449400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>195400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>246400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>254400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>389400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>62300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>179300</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
@@ -6125,110 +6259,113 @@
       <c r="AO58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>319500</v>
+      </c>
+      <c r="E59" s="3">
         <v>634500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>299400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>300700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>294200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>616300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>327500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>328300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>316600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>572200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>263800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>246600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="3">
         <v>944600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>941200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>890900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>862000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>889700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>868300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>809500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>802800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>783100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>774300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>759500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>714400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>671600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>629100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>617200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>607000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>506400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>487900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>475600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>461200</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK59" s="3" t="s">
         <v>8</v>
       </c>
@@ -6244,110 +6381,113 @@
       <c r="AO59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3044900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2670200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2699700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2434200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2510400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2534100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2742000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2523800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2525800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2468000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2739100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2591100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2619300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2545300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2600000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2484100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2209100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2002500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2104100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1839200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2035900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2031200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2210400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1764200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1720200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1801400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2051800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1611100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1673900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1577700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1853800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1321000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1440000</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK60" s="3" t="s">
         <v>8</v>
       </c>
@@ -6363,110 +6503,113 @@
       <c r="AO60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2304500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2396800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2319200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2358300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2376100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2476400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2423400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2456700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2468100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2511800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2483100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2523200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2485800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>447900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>600100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>699400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>749000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>748600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>748100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>747700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>747300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>846200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>845700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1202200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1334800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1337300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1339700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1540600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1543500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1546500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1549400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1894100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2508000</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
@@ -6482,110 +6625,113 @@
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>382900</v>
+      </c>
+      <c r="E62" s="3">
         <v>162800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>283900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>269900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>241900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>132200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>219100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>218900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>222700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>143500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>189100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>194200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>190900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2309900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2335900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2350100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2330600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2269700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2290300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2272300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2252400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2214800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2208800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2208500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2240600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2185400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2191100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2165000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2157600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>317200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>318400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>323700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>324700</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6601,8 +6747,11 @@
       <c r="AO62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6720,8 +6869,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6839,8 +6991,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6958,110 +7113,113 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5802700</v>
+      </c>
+      <c r="E66" s="3">
         <v>5312800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5373900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5132700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5186100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5217900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5454100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5275000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5297300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5218800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5483500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5372600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5362800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5303100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5536000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5533700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5288700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5020800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5142500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4859200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5035700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5092200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5264900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5174900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5295600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5324100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5582600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5316700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5375000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3441400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3721600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3538700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4272700</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>8</v>
       </c>
@@ -7077,8 +7235,11 @@
       <c r="AO66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7120,8 +7281,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7239,8 +7401,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7358,8 +7523,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7477,8 +7645,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7596,110 +7767,113 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1343900</v>
+      </c>
+      <c r="E72" s="3">
         <v>1201200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2155200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2003100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1852400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1702600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1580000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1424200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1279300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1168200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1022400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>891900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>760600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>644500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>514700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>384800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>243800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>131300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>23700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-102800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-213800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-295300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-391200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-514000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-620600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-716400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-758100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-813200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-867700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-915100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-979400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-1033900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-1028200</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7715,8 +7889,11 @@
       <c r="AO72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7834,8 +8011,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7953,8 +8133,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8072,110 +8255,113 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2126300</v>
+      </c>
+      <c r="E76" s="3">
         <v>2197700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2171900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2099100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1971600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1847500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1762200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1654900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1527400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1458900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1353700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1231300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1131700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1046800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>942900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>853600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>721300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>648100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>567700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>488400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>413500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>319300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>217400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>119100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>32500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-54300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-104500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-164600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-148300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-202100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-256600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-317900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-1011400</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>8</v>
       </c>
@@ -8191,8 +8377,11 @@
       <c r="AO76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8310,251 +8499,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46144</v>
+      </c>
+      <c r="E80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45962</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45871</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45780</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45689</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45598</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45507</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45416</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45325</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45227</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45136</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45045</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44954</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44863</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44772</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44590</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44499</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44317</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44226</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44044</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43953</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43862</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43771</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43680</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43589</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43498</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43407</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43316</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43134</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43036</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42945</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42854</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42763</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>142700</v>
+      </c>
+      <c r="E81" s="3">
         <v>125900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>152100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>150700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>149800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>122700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>155700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>145000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>111000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>145900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>130500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>131300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>116100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>129800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>129900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>141000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>112500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>107600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>126500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>111000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>81600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>95900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>122800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>106600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>95700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>41800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>55100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>54500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>35800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>64300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>54400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>66700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>22800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>19700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-58900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>16600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8596,127 +8794,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E83" s="3">
         <v>61300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>65700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>65100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>63400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>53400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>57400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>54800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>54200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>42500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>52200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>50000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>47100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>51700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>52200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>50000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>47100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>44900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>45800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>45400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>44400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>43100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>42200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>41300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>40800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>40100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>39200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>39000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>38700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>39800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>39900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>41100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>41400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>40700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>41100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>41200</v>
       </c>
-      <c r="AM83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO83" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP83" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8834,8 +9036,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8953,8 +9158,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9072,8 +9280,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9191,8 +9402,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9310,127 +9524,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E89" s="3">
         <v>391000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>181100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>249900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>208100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>271900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>206800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>221400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>200800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>274400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>175000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>150400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>119100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>175300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>169800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>398700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>44300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>98500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>173900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>310300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>249000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>66600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>68300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>263800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>469900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>133600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>170200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>44900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>176200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>47700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>137900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>65400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>109700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>46400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>119100</v>
       </c>
-      <c r="AM89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO89" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP89" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9472,127 +9692,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-182000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-201100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-194900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-165600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-140500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-160400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-187900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-133900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-105700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-119100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-133700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-122200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-92100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-103500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-102800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-101000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-90500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-101100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-74700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-73100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-74700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-65500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-69800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-47800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-35200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-52500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-56100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-51800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-36500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-42600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-27700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-51300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-21800</v>
       </c>
-      <c r="AM91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO91" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP91" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9710,8 +9934,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9829,127 +10056,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-184600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-201200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-195000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-163900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-142300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-162000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-187900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-133900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-105700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-119100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-127400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-116200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-92100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-87300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-94400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-474800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-90500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-101100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-74700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-70700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-58100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-65500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-48000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-43700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-35200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-30900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-56100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-51800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-36500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-33500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-42100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-51300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-39900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-21800</v>
       </c>
-      <c r="AM94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO94" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP94" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9991,8 +10224,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10020,11 +10254,11 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>8</v>
@@ -10032,8 +10266,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10096,22 +10330,25 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-100</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
         <v>0</v>
       </c>
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10229,8 +10466,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10348,8 +10588,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10467,127 +10710,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-188700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>11700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-78200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-54600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-115500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-23000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-84500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-96100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-152700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-40300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-31400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-37600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-88700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-204500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>201800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>38700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-36600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-56900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-260200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-171500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-143000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-184200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-332000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-102500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>50600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-119200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-138000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-103500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-27700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-96100</v>
       </c>
-      <c r="AM100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO100" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP100" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10627,8 +10876,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10705,123 +10954,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E102" s="3">
         <v>1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-129000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>125700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-39300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>42300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-20500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>19400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-122700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>35900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>102700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>3200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1200</v>
       </c>
-      <c r="AM102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AO102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
